--- a/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results.xlsx
+++ b/Output Files GPT-OSS 20B/LLM-Parameterized_Reference_Scoring_results.xlsx
@@ -613,7 +613,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K2" t="n">
         <v>13</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="X2" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="Z2" t="n">
         <v>0.7</v>
@@ -664,7 +664,7 @@
         <v>3</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7484999999999999</v>
+        <v>0.768</v>
       </c>
       <c r="AD2" t="n">
         <v>1</v>
@@ -711,7 +711,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K3" t="n">
         <v>13</v>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="X3" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.8320000000000001</v>
+        <v>0.845</v>
       </c>
       <c r="AD3" t="n">
         <v>1</v>
@@ -809,7 +809,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K4" t="n">
         <v>13</v>
@@ -845,10 +845,10 @@
         </is>
       </c>
       <c r="X4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="Z4" t="n">
         <v>0.7</v>
@@ -860,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.798</v>
       </c>
       <c r="AD4" t="n">
         <v>1</v>
@@ -1201,10 +1201,10 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>35</v>
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="X8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="Z8" t="n">
         <v>0.93</v>
@@ -1252,7 +1252,7 @@
         <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.6659999999999999</v>
+        <v>0.6465000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1299,10 +1299,10 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L9" t="n">
         <v>35</v>
@@ -1335,10 +1335,10 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="Z9" t="n">
         <v>0.7</v>
@@ -1350,7 +1350,7 @@
         <v>2</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.6459999999999999</v>
+        <v>0.6199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
@@ -1397,10 +1397,10 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
         <v>35</v>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="X10" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.65</v>
+        <v>0.6</v>
       </c>
       <c r="Z10" t="n">
         <v>0.41</v>
@@ -1448,7 +1448,7 @@
         <v>3</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.6034999999999999</v>
+        <v>0.5740000000000001</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -1495,13 +1495,13 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
         <v>13</v>
       </c>
       <c r="L11" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1531,22 +1531,22 @@
         </is>
       </c>
       <c r="X11" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="Z11" t="n">
         <v>0.61</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="AB11" t="n">
         <v>3</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.7885000000000001</v>
+        <v>0.6964999999999999</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
@@ -1593,13 +1593,13 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
         <v>13</v>
       </c>
       <c r="L12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1629,22 +1629,22 @@
         </is>
       </c>
       <c r="X12" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="Z12" t="n">
         <v>0.86</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="AB12" t="n">
         <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.7204999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
@@ -1691,13 +1691,13 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
         <v>13</v>
       </c>
       <c r="L13" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="X13" t="n">
-        <v>0.82</v>
+        <v>0.67</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.82</v>
+        <v>0.68</v>
       </c>
       <c r="Z13" t="n">
         <v>0.93</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.63</v>
+        <v>0.58</v>
       </c>
       <c r="AB13" t="n">
         <v>2</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.8135</v>
+        <v>0.712</v>
       </c>
       <c r="AD13" t="n">
         <v>1</v>
@@ -1803,7 +1803,7 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>unoccupied_18</t>
+          <t>unoccupied_16</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="X14" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="Z14" t="n">
         <v>0.86</v>
@@ -1840,7 +1840,7 @@
         <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.8470000000000001</v>
+        <v>0.8340000000000001</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
@@ -1901,7 +1901,7 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>unoccupied_18</t>
+          <t>unoccupied_16</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -1923,10 +1923,10 @@
         </is>
       </c>
       <c r="X15" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="Z15" t="n">
         <v>0.93</v>
@@ -1938,7 +1938,7 @@
         <v>1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.875</v>
+        <v>0.8620000000000001</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>unoccupied_18</t>
+          <t>unoccupied_16</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="X16" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="Z16" t="n">
         <v>0.7</v>
@@ -2036,7 +2036,7 @@
         <v>3</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.839</v>
+        <v>0.829</v>
       </c>
       <c r="AD16" t="n">
         <v>1</v>
@@ -2677,7 +2677,7 @@
         <v>13</v>
       </c>
       <c r="L23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -2716,13 +2716,13 @@
         <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AB23" t="n">
         <v>1</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7444999999999999</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -2775,7 +2775,7 @@
         <v>13</v>
       </c>
       <c r="L24" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
@@ -2814,13 +2814,13 @@
         <v>0.78</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="AB24" t="n">
         <v>2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.726</v>
+        <v>0.7230000000000001</v>
       </c>
       <c r="AD24" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
         <v>13</v>
       </c>
       <c r="L25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
@@ -2912,13 +2912,13 @@
         <v>0.51</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="AB25" t="n">
         <v>3</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.6975</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="AD25" t="n">
         <v>1</v>
@@ -2965,13 +2965,13 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K26" t="n">
         <v>13</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="X26" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="Z26" t="n">
         <v>0.78</v>
@@ -3016,7 +3016,7 @@
         <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>0.8595</v>
+        <v>0.8530000000000001</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
@@ -3063,13 +3063,13 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K27" t="n">
         <v>13</v>
       </c>
       <c r="L27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="X27" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="Z27" t="n">
         <v>1</v>
@@ -3114,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.8905000000000001</v>
+        <v>0.8839999999999999</v>
       </c>
       <c r="AD27" t="n">
         <v>1</v>
@@ -3161,13 +3161,13 @@
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
         <v>13</v>
       </c>
       <c r="L28" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3197,10 +3197,10 @@
         </is>
       </c>
       <c r="X28" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="Z28" t="n">
         <v>0.78</v>
@@ -3212,7 +3212,7 @@
         <v>3</v>
       </c>
       <c r="AC28" t="n">
-        <v>0.83</v>
+        <v>0.8205</v>
       </c>
       <c r="AD28" t="n">
         <v>1</v>
@@ -3850,7 +3850,7 @@
         <v>13</v>
       </c>
       <c r="K35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L35" t="n">
         <v>3</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="X35" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="Y35" t="n">
         <v>0.97</v>
@@ -3898,7 +3898,7 @@
         <v>3</v>
       </c>
       <c r="AC35" t="n">
-        <v>0.883</v>
+        <v>0.88</v>
       </c>
       <c r="AD35" t="n">
         <v>1</v>
@@ -3948,7 +3948,7 @@
         <v>13</v>
       </c>
       <c r="K36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L36" t="n">
         <v>3</v>
@@ -3984,7 +3984,7 @@
         <v>0.96</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="Z36" t="n">
         <v>0.93</v>
@@ -3996,7 +3996,7 @@
         <v>1</v>
       </c>
       <c r="AC36" t="n">
-        <v>0.9195</v>
+        <v>0.916</v>
       </c>
       <c r="AD36" t="n">
         <v>1</v>
@@ -4046,7 +4046,7 @@
         <v>13</v>
       </c>
       <c r="K37" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L37" t="n">
         <v>3</v>
@@ -4079,10 +4079,10 @@
         </is>
       </c>
       <c r="X37" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="Z37" t="n">
         <v>0.86</v>
@@ -4094,7 +4094,7 @@
         <v>2</v>
       </c>
       <c r="AC37" t="n">
-        <v>0.8955</v>
+        <v>0.889</v>
       </c>
       <c r="AD37" t="n">
         <v>1</v>
@@ -4144,7 +4144,7 @@
         <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L38" t="n">
         <v>3</v>
@@ -4177,10 +4177,10 @@
         </is>
       </c>
       <c r="X38" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="Z38" t="n">
         <v>1</v>
@@ -4192,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="AC38" t="n">
-        <v>0.8494999999999999</v>
+        <v>0.8399999999999999</v>
       </c>
       <c r="AD38" t="n">
         <v>1</v>
@@ -4242,7 +4242,7 @@
         <v>13</v>
       </c>
       <c r="K39" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L39" t="n">
         <v>3</v>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="X39" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="Z39" t="n">
         <v>0.73</v>
@@ -4290,7 +4290,7 @@
         <v>2</v>
       </c>
       <c r="AC39" t="n">
-        <v>0.8055000000000001</v>
+        <v>0.7955000000000001</v>
       </c>
       <c r="AD39" t="n">
         <v>1</v>
@@ -4340,7 +4340,7 @@
         <v>13</v>
       </c>
       <c r="K40" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L40" t="n">
         <v>3</v>
@@ -4373,10 +4373,10 @@
         </is>
       </c>
       <c r="X40" t="n">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="Z40" t="n">
         <v>0.38</v>
@@ -4388,7 +4388,7 @@
         <v>3</v>
       </c>
       <c r="AC40" t="n">
-        <v>0.7449999999999999</v>
+        <v>0.7355</v>
       </c>
       <c r="AD40" t="n">
         <v>1</v>
@@ -5037,7 +5037,7 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="R47" t="inlineStr"/>
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="X47" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="Z47" t="n">
         <v>0.61</v>
@@ -5074,7 +5074,7 @@
         <v>3</v>
       </c>
       <c r="AC47" t="n">
-        <v>0.719</v>
+        <v>0.7254999999999999</v>
       </c>
       <c r="AD47" t="n">
         <v>1</v>
@@ -5135,7 +5135,7 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="R48" t="inlineStr"/>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="X48" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="Y48" t="n">
         <v>0.72</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0.71</v>
       </c>
       <c r="Z48" t="n">
         <v>0.86</v>
@@ -5172,7 +5172,7 @@
         <v>1</v>
       </c>
       <c r="AC48" t="n">
-        <v>0.746</v>
+        <v>0.7525000000000001</v>
       </c>
       <c r="AD48" t="n">
         <v>1</v>
@@ -5233,7 +5233,7 @@
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="R49" t="inlineStr"/>
@@ -5255,10 +5255,10 @@
         </is>
       </c>
       <c r="X49" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z49" t="n">
         <v>0.93</v>
@@ -5270,7 +5270,7 @@
         <v>2</v>
       </c>
       <c r="AC49" t="n">
-        <v>0.7375</v>
+        <v>0.744</v>
       </c>
       <c r="AD49" t="n">
         <v>1</v>
@@ -5331,7 +5331,7 @@
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>occupied_all_day</t>
+          <t>unoccupied_8</t>
         </is>
       </c>
       <c r="R50" t="inlineStr"/>
@@ -5353,10 +5353,10 @@
         </is>
       </c>
       <c r="X50" t="n">
-        <v>0.63</v>
+        <v>0.72</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
       <c r="Z50" t="n">
         <v>0.93</v>
@@ -5368,7 +5368,7 @@
         <v>2</v>
       </c>
       <c r="AC50" t="n">
-        <v>0.7355</v>
+        <v>0.7869999999999999</v>
       </c>
       <c r="AD50" t="n">
         <v>1</v>
@@ -5429,7 +5429,7 @@
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>occupied_all_day</t>
+          <t>unoccupied_8</t>
         </is>
       </c>
       <c r="R51" t="inlineStr"/>
@@ -5451,10 +5451,10 @@
         </is>
       </c>
       <c r="X51" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="Z51" t="n">
         <v>0.86</v>
@@ -5466,7 +5466,7 @@
         <v>1</v>
       </c>
       <c r="AC51" t="n">
-        <v>0.7475000000000001</v>
+        <v>0.7925</v>
       </c>
       <c r="AD51" t="n">
         <v>1</v>
@@ -5527,7 +5527,7 @@
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>occupied_all_day</t>
+          <t>unoccupied_8</t>
         </is>
       </c>
       <c r="R52" t="inlineStr"/>
@@ -5549,10 +5549,10 @@
         </is>
       </c>
       <c r="X52" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="Z52" t="n">
         <v>0.61</v>
@@ -5564,7 +5564,7 @@
         <v>3</v>
       </c>
       <c r="AC52" t="n">
-        <v>0.72</v>
+        <v>0.762</v>
       </c>
       <c r="AD52" t="n">
         <v>1</v>
@@ -6199,13 +6199,13 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="n">
+        <v>13</v>
+      </c>
+      <c r="K59" t="n">
         <v>14</v>
       </c>
-      <c r="K59" t="n">
-        <v>13</v>
-      </c>
       <c r="L59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
@@ -6235,22 +6235,22 @@
         </is>
       </c>
       <c r="X59" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.61</v>
+        <v>0.59</v>
       </c>
       <c r="Z59" t="n">
         <v>0.63</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AB59" t="n">
         <v>2</v>
       </c>
       <c r="AC59" t="n">
-        <v>0.62</v>
+        <v>0.6114999999999999</v>
       </c>
       <c r="AD59" t="n">
         <v>1</v>
@@ -6297,13 +6297,13 @@
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="n">
+        <v>13</v>
+      </c>
+      <c r="K60" t="n">
         <v>14</v>
       </c>
-      <c r="K60" t="n">
-        <v>13</v>
-      </c>
       <c r="L60" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
@@ -6333,22 +6333,22 @@
         </is>
       </c>
       <c r="X60" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="Z60" t="n">
         <v>0.92</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AB60" t="n">
         <v>1</v>
       </c>
       <c r="AC60" t="n">
-        <v>0.6455000000000001</v>
+        <v>0.6405000000000001</v>
       </c>
       <c r="AD60" t="n">
         <v>1</v>
@@ -6395,13 +6395,13 @@
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="n">
+        <v>13</v>
+      </c>
+      <c r="K61" t="n">
         <v>14</v>
       </c>
-      <c r="K61" t="n">
-        <v>13</v>
-      </c>
       <c r="L61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
@@ -6431,22 +6431,22 @@
         </is>
       </c>
       <c r="X61" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.51</v>
+        <v>0.5</v>
       </c>
       <c r="Z61" t="n">
         <v>0.83</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AB61" t="n">
         <v>3</v>
       </c>
       <c r="AC61" t="n">
-        <v>0.5980000000000001</v>
+        <v>0.593</v>
       </c>
       <c r="AD61" t="n">
         <v>1</v>
@@ -6787,7 +6787,7 @@
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K65" t="n">
         <v>13</v>
@@ -6823,10 +6823,10 @@
         </is>
       </c>
       <c r="X65" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="Z65" t="n">
         <v>0.92</v>
@@ -6838,7 +6838,7 @@
         <v>2</v>
       </c>
       <c r="AC65" t="n">
-        <v>0.5965</v>
+        <v>0.6095</v>
       </c>
       <c r="AD65" t="n">
         <v>1</v>
@@ -6885,7 +6885,7 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K66" t="n">
         <v>13</v>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="X66" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="Z66" t="n">
         <v>0.83</v>
@@ -6936,7 +6936,7 @@
         <v>1</v>
       </c>
       <c r="AC66" t="n">
-        <v>0.6154999999999999</v>
+        <v>0.6220000000000001</v>
       </c>
       <c r="AD66" t="n">
         <v>1</v>
@@ -6983,7 +6983,7 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K67" t="n">
         <v>13</v>
@@ -7019,10 +7019,10 @@
         </is>
       </c>
       <c r="X67" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="Z67" t="n">
         <v>0.51</v>
@@ -7034,7 +7034,7 @@
         <v>3</v>
       </c>
       <c r="AC67" t="n">
-        <v>0.5805</v>
+        <v>0.587</v>
       </c>
       <c r="AD67" t="n">
         <v>1</v>
@@ -7081,7 +7081,7 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K68" t="n">
         <v>13</v>
@@ -7117,10 +7117,10 @@
         </is>
       </c>
       <c r="X68" t="n">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="Y68" t="n">
-        <v>0.6</v>
+        <v>0.79</v>
       </c>
       <c r="Z68" t="n">
         <v>0.59</v>
@@ -7132,7 +7132,7 @@
         <v>2</v>
       </c>
       <c r="AC68" t="n">
-        <v>0.604</v>
+        <v>0.7274999999999999</v>
       </c>
       <c r="AD68" t="n">
         <v>1</v>
@@ -7179,7 +7179,7 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K69" t="n">
         <v>13</v>
@@ -7215,10 +7215,10 @@
         </is>
       </c>
       <c r="X69" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="Y69" t="n">
-        <v>0.55</v>
+        <v>0.76</v>
       </c>
       <c r="Z69" t="n">
         <v>0.91</v>
@@ -7230,7 +7230,7 @@
         <v>1</v>
       </c>
       <c r="AC69" t="n">
-        <v>0.6355000000000001</v>
+        <v>0.7689999999999999</v>
       </c>
       <c r="AD69" t="n">
         <v>1</v>
@@ -7277,7 +7277,7 @@
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K70" t="n">
         <v>13</v>
@@ -7313,10 +7313,10 @@
         </is>
       </c>
       <c r="X70" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="Y70" t="n">
-        <v>0.51</v>
+        <v>0.72</v>
       </c>
       <c r="Z70" t="n">
         <v>0.8100000000000001</v>
@@ -7328,7 +7328,7 @@
         <v>3</v>
       </c>
       <c r="AC70" t="n">
-        <v>0.5865</v>
+        <v>0.726</v>
       </c>
       <c r="AD70" t="n">
         <v>1</v>
@@ -7669,7 +7669,7 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K74" t="n">
         <v>10</v>
@@ -7705,10 +7705,10 @@
         </is>
       </c>
       <c r="X74" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Y74" t="n">
         <v>0.14</v>
-      </c>
-      <c r="Y74" t="n">
-        <v>0.16</v>
       </c>
       <c r="Z74" t="n">
         <v>1</v>
@@ -7717,10 +7717,10 @@
         <v>0.79</v>
       </c>
       <c r="AB74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC74" t="n">
-        <v>0.4165</v>
+        <v>0.4005</v>
       </c>
       <c r="AD74" t="n">
         <v>1</v>
@@ -7767,7 +7767,7 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K75" t="n">
         <v>10</v>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="X75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="Y75" t="n">
         <v>0.21</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>0.23</v>
       </c>
       <c r="Z75" t="n">
         <v>0.78</v>
@@ -7818,7 +7818,7 @@
         <v>1</v>
       </c>
       <c r="AC75" t="n">
-        <v>0.418</v>
+        <v>0.405</v>
       </c>
       <c r="AD75" t="n">
         <v>1</v>
@@ -7865,7 +7865,7 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K76" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
         </is>
       </c>
       <c r="X76" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Y76" t="n">
         <v>0.28</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>0.29</v>
       </c>
       <c r="Z76" t="n">
         <v>0.51</v>
@@ -7913,10 +7913,10 @@
         <v>0.82</v>
       </c>
       <c r="AB76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC76" t="n">
-        <v>0.4105</v>
+        <v>0.404</v>
       </c>
       <c r="AD76" t="n">
         <v>1</v>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -8256,68 +8256,58 @@
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="n">
-        <v>13</v>
-      </c>
-      <c r="K80" t="n">
-        <v>13</v>
-      </c>
-      <c r="L80" t="n">
-        <v>20</v>
-      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>occupied_sleep</t>
-        </is>
-      </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr">
         <is>
-          <t>HVACGroundTruthCalculator</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="U80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V80" t="b">
         <v>0</v>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>Alternative 1 (extraction failed)</t>
         </is>
       </c>
       <c r="X80" t="n">
-        <v>0.6899999999999999</v>
+        <v>1928</v>
       </c>
       <c r="Y80" t="n">
-        <v>0.71</v>
+        <v>1928</v>
       </c>
       <c r="Z80" t="n">
-        <v>0.7</v>
+        <v>1928</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.63</v>
+        <v>1928</v>
       </c>
       <c r="AB80" t="n">
-        <v>2</v>
+        <v>1928</v>
       </c>
       <c r="AC80" t="n">
-        <v>0.6899999999999999</v>
+        <v>1928</v>
       </c>
       <c r="AD80" t="n">
         <v>1</v>
       </c>
       <c r="AE80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -8346,7 +8336,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -8354,68 +8344,58 @@
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="n">
-        <v>13</v>
-      </c>
-      <c r="K81" t="n">
-        <v>13</v>
-      </c>
-      <c r="L81" t="n">
-        <v>20</v>
-      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>occupied_sleep</t>
-        </is>
-      </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr">
         <is>
-          <t>HVACGroundTruthCalculator</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="U81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V81" t="b">
         <v>0</v>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>Alternative 2 (extraction failed)</t>
         </is>
       </c>
       <c r="X81" t="n">
-        <v>0.65</v>
+        <v>1928</v>
       </c>
       <c r="Y81" t="n">
-        <v>0.67</v>
+        <v>1928</v>
       </c>
       <c r="Z81" t="n">
-        <v>0.93</v>
+        <v>1928</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.63</v>
+        <v>1928</v>
       </c>
       <c r="AB81" t="n">
-        <v>1</v>
+        <v>1928</v>
       </c>
       <c r="AC81" t="n">
-        <v>0.7100000000000001</v>
+        <v>1928</v>
       </c>
       <c r="AD81" t="n">
         <v>1</v>
       </c>
       <c r="AE81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -8444,7 +8424,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -8452,68 +8432,58 @@
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="n">
-        <v>13</v>
-      </c>
-      <c r="K82" t="n">
-        <v>13</v>
-      </c>
-      <c r="L82" t="n">
-        <v>20</v>
-      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr">
-        <is>
-          <t>occupied_sleep</t>
-        </is>
-      </c>
+      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr">
         <is>
-          <t>HVACGroundTruthCalculator</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="U82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V82" t="b">
         <v>0</v>
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>Alternative 3 (extraction failed)</t>
         </is>
       </c>
       <c r="X82" t="n">
-        <v>0.61</v>
+        <v>1928</v>
       </c>
       <c r="Y82" t="n">
-        <v>0.64</v>
+        <v>1928</v>
       </c>
       <c r="Z82" t="n">
-        <v>0.86</v>
+        <v>1928</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.63</v>
+        <v>1928</v>
       </c>
       <c r="AB82" t="n">
-        <v>3</v>
+        <v>1928</v>
       </c>
       <c r="AC82" t="n">
-        <v>0.6735</v>
+        <v>1928</v>
       </c>
       <c r="AD82" t="n">
         <v>1</v>
       </c>
       <c r="AE82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -8551,7 +8521,7 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K83" t="n">
         <v>13</v>
@@ -8587,10 +8557,10 @@
         </is>
       </c>
       <c r="X83" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="Y83" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="Z83" t="n">
         <v>0.85</v>
@@ -8599,10 +8569,10 @@
         <v>0.68</v>
       </c>
       <c r="AB83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC83" t="n">
-        <v>0.4285</v>
+        <v>0.4835</v>
       </c>
       <c r="AD83" t="n">
         <v>1</v>
@@ -8649,7 +8619,7 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K84" t="n">
         <v>13</v>
@@ -8685,10 +8655,10 @@
         </is>
       </c>
       <c r="X84" t="n">
-        <v>0.27</v>
+        <v>0.35</v>
       </c>
       <c r="Y84" t="n">
-        <v>0.29</v>
+        <v>0.36</v>
       </c>
       <c r="Z84" t="n">
         <v>0.67</v>
@@ -8697,10 +8667,10 @@
         <v>0.75</v>
       </c>
       <c r="AB84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC84" t="n">
-        <v>0.429</v>
+        <v>0.4775</v>
       </c>
       <c r="AD84" t="n">
         <v>1</v>
@@ -8747,7 +8717,7 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="K85" t="n">
         <v>13</v>
@@ -8783,10 +8753,10 @@
         </is>
       </c>
       <c r="X85" t="n">
-        <v>0.31</v>
+        <v>0.38</v>
       </c>
       <c r="Y85" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="Z85" t="n">
         <v>0.45</v>
@@ -8798,7 +8768,7 @@
         <v>3</v>
       </c>
       <c r="AC85" t="n">
-        <v>0.4075</v>
+        <v>0.453</v>
       </c>
       <c r="AD85" t="n">
         <v>1</v>
@@ -8845,13 +8815,13 @@
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K86" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L86" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
@@ -8881,22 +8851,22 @@
         </is>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Z86" t="n">
         <v>0.73</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB86" t="n">
         <v>1</v>
       </c>
       <c r="AC86" t="n">
-        <v>0.2585</v>
+        <v>0.3945</v>
       </c>
       <c r="AD86" t="n">
         <v>1</v>
@@ -8943,13 +8913,13 @@
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr"/>
       <c r="J87" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K87" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L87" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
@@ -8979,22 +8949,22 @@
         </is>
       </c>
       <c r="X87" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="Z87" t="n">
         <v>0.51</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AB87" t="n">
         <v>2</v>
       </c>
       <c r="AC87" t="n">
-        <v>0.2145</v>
+        <v>0.3765</v>
       </c>
       <c r="AD87" t="n">
         <v>1</v>
@@ -9041,13 +9011,13 @@
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
       <c r="J88" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K88" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L88" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
@@ -9077,22 +9047,22 @@
         </is>
       </c>
       <c r="X88" t="n">
-        <v>0.01</v>
+        <v>0.27</v>
       </c>
       <c r="Y88" t="n">
-        <v>0.03</v>
+        <v>0.28</v>
       </c>
       <c r="Z88" t="n">
         <v>0.23</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.66</v>
+        <v>0.71</v>
       </c>
       <c r="AB88" t="n">
         <v>3</v>
       </c>
       <c r="AC88" t="n">
-        <v>0.1585</v>
+        <v>0.3315</v>
       </c>
       <c r="AD88" t="n">
         <v>1</v>
@@ -9139,13 +9109,13 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr"/>
       <c r="J89" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K89" t="n">
         <v>13</v>
       </c>
       <c r="L89" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
@@ -9175,22 +9145,22 @@
         </is>
       </c>
       <c r="X89" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Y89" t="n">
         <v>0.5</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>0.51</v>
       </c>
       <c r="Z89" t="n">
         <v>0.93</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AB89" t="n">
         <v>1</v>
       </c>
       <c r="AC89" t="n">
-        <v>0.639</v>
+        <v>0.631</v>
       </c>
       <c r="AD89" t="n">
         <v>1</v>
@@ -9237,13 +9207,13 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr"/>
       <c r="J90" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K90" t="n">
         <v>13</v>
       </c>
       <c r="L90" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
@@ -9273,22 +9243,22 @@
         </is>
       </c>
       <c r="X90" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Y90" t="n">
         <v>0.53</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>0.54</v>
       </c>
       <c r="Z90" t="n">
         <v>0.78</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AB90" t="n">
         <v>2</v>
       </c>
       <c r="AC90" t="n">
-        <v>0.6284999999999999</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="AD90" t="n">
         <v>1</v>
@@ -9335,13 +9305,13 @@
       <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr"/>
       <c r="J91" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K91" t="n">
         <v>13</v>
       </c>
       <c r="L91" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
@@ -9371,7 +9341,7 @@
         </is>
       </c>
       <c r="X91" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="Y91" t="n">
         <v>0.5600000000000001</v>
@@ -9380,13 +9350,13 @@
         <v>0.61</v>
       </c>
       <c r="AA91" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="AB91" t="n">
         <v>3</v>
       </c>
       <c r="AC91" t="n">
-        <v>0.6104999999999999</v>
+        <v>0.606</v>
       </c>
       <c r="AD91" t="n">
         <v>1</v>
@@ -9433,10 +9403,10 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="J92" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L92" t="n">
         <v>8</v>
@@ -9469,10 +9439,10 @@
         </is>
       </c>
       <c r="X92" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="Y92" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="Z92" t="n">
         <v>0.45</v>
@@ -9484,7 +9454,7 @@
         <v>3</v>
       </c>
       <c r="AC92" t="n">
-        <v>0.503</v>
+        <v>0.529</v>
       </c>
       <c r="AD92" t="n">
         <v>1</v>
@@ -9531,10 +9501,10 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K93" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L93" t="n">
         <v>8</v>
@@ -9567,10 +9537,10 @@
         </is>
       </c>
       <c r="X93" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y93" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z93" t="n">
         <v>1</v>
@@ -9582,7 +9552,7 @@
         <v>1</v>
       </c>
       <c r="AC93" t="n">
-        <v>0.675</v>
+        <v>0.6945000000000001</v>
       </c>
       <c r="AD93" t="n">
         <v>1</v>
@@ -9629,10 +9599,10 @@
       <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K94" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L94" t="n">
         <v>8</v>
@@ -9665,10 +9635,10 @@
         </is>
       </c>
       <c r="X94" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="Y94" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="Z94" t="n">
         <v>0.45</v>
@@ -9680,7 +9650,7 @@
         <v>2</v>
       </c>
       <c r="AC94" t="n">
-        <v>0.61</v>
+        <v>0.6295000000000001</v>
       </c>
       <c r="AD94" t="n">
         <v>1</v>
@@ -9727,7 +9697,7 @@
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
       <c r="J95" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K95" t="n">
         <v>13</v>
@@ -9763,10 +9733,10 @@
         </is>
       </c>
       <c r="X95" t="n">
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="Y95" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="Z95" t="n">
         <v>0.86</v>
@@ -9778,7 +9748,7 @@
         <v>1</v>
       </c>
       <c r="AC95" t="n">
-        <v>0.4365</v>
+        <v>0.4525</v>
       </c>
       <c r="AD95" t="n">
         <v>1</v>
@@ -9825,7 +9795,7 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K96" t="n">
         <v>13</v>
@@ -9861,10 +9831,10 @@
         </is>
       </c>
       <c r="X96" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="Y96" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="Z96" t="n">
         <v>0.7</v>
@@ -9876,7 +9846,7 @@
         <v>2</v>
       </c>
       <c r="AC96" t="n">
-        <v>0.4269999999999999</v>
+        <v>0.4435</v>
       </c>
       <c r="AD96" t="n">
         <v>1</v>
@@ -9923,7 +9893,7 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr"/>
       <c r="J97" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K97" t="n">
         <v>13</v>
@@ -9959,10 +9929,10 @@
         </is>
       </c>
       <c r="X97" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="Y97" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="Z97" t="n">
         <v>0.51</v>
@@ -9974,7 +9944,7 @@
         <v>3</v>
       </c>
       <c r="AC97" t="n">
-        <v>0.412</v>
+        <v>0.425</v>
       </c>
       <c r="AD97" t="n">
         <v>1</v>
@@ -10315,10 +10285,10 @@
       <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K101" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L101" t="n">
         <v>35</v>
@@ -10351,10 +10321,10 @@
         </is>
       </c>
       <c r="X101" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="Y101" t="n">
-        <v>0.51</v>
+        <v>0.58</v>
       </c>
       <c r="Z101" t="n">
         <v>0.86</v>
@@ -10366,7 +10336,7 @@
         <v>1</v>
       </c>
       <c r="AC101" t="n">
-        <v>0.6160000000000001</v>
+        <v>0.6615</v>
       </c>
       <c r="AD101" t="n">
         <v>1</v>
@@ -10413,10 +10383,10 @@
       <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="J102" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K102" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L102" t="n">
         <v>35</v>
@@ -10449,10 +10419,10 @@
         </is>
       </c>
       <c r="X102" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="Y102" t="n">
-        <v>0.54</v>
+        <v>0.61</v>
       </c>
       <c r="Z102" t="n">
         <v>0.7</v>
@@ -10464,7 +10434,7 @@
         <v>2</v>
       </c>
       <c r="AC102" t="n">
-        <v>0.608</v>
+        <v>0.6535</v>
       </c>
       <c r="AD102" t="n">
         <v>1</v>
@@ -10511,10 +10481,10 @@
       <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K103" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L103" t="n">
         <v>35</v>
@@ -10547,10 +10517,10 @@
         </is>
       </c>
       <c r="X103" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="Y103" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="Z103" t="n">
         <v>0.51</v>
@@ -10562,7 +10532,7 @@
         <v>3</v>
       </c>
       <c r="AC103" t="n">
-        <v>0.583</v>
+        <v>0.635</v>
       </c>
       <c r="AD103" t="n">
         <v>1</v>
@@ -10909,7 +10879,7 @@
         <v>13</v>
       </c>
       <c r="L107" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
@@ -10948,13 +10918,13 @@
         <v>0.78</v>
       </c>
       <c r="AA107" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AB107" t="n">
         <v>3</v>
       </c>
       <c r="AC107" t="n">
-        <v>0.6815</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="AD107" t="n">
         <v>1</v>
@@ -11007,7 +10977,7 @@
         <v>13</v>
       </c>
       <c r="L108" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
@@ -11046,13 +11016,13 @@
         <v>1</v>
       </c>
       <c r="AA108" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="AB108" t="n">
         <v>2</v>
       </c>
       <c r="AC108" t="n">
-        <v>0.758</v>
+        <v>0.7565</v>
       </c>
       <c r="AD108" t="n">
         <v>1</v>
@@ -11105,7 +11075,7 @@
         <v>13</v>
       </c>
       <c r="L109" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
@@ -11491,7 +11461,7 @@
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K113" t="n">
         <v>13</v>
@@ -11589,7 +11559,7 @@
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K114" t="n">
         <v>13</v>
@@ -11687,7 +11657,7 @@
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="K115" t="n">
         <v>13</v>
@@ -11788,7 +11758,7 @@
         <v>13</v>
       </c>
       <c r="K116" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L116" t="n">
         <v>25</v>
@@ -11821,10 +11791,10 @@
         </is>
       </c>
       <c r="X116" t="n">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="Y116" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="Z116" t="n">
         <v>0.61</v>
@@ -11836,7 +11806,7 @@
         <v>2</v>
       </c>
       <c r="AC116" t="n">
-        <v>0.8345</v>
+        <v>0.8115</v>
       </c>
       <c r="AD116" t="n">
         <v>1</v>
@@ -11886,7 +11856,7 @@
         <v>13</v>
       </c>
       <c r="K117" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L117" t="n">
         <v>25</v>
@@ -11919,10 +11889,10 @@
         </is>
       </c>
       <c r="X117" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="Y117" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="Z117" t="n">
         <v>0.86</v>
@@ -11934,7 +11904,7 @@
         <v>1</v>
       </c>
       <c r="AC117" t="n">
-        <v>0.8520000000000001</v>
+        <v>0.8195</v>
       </c>
       <c r="AD117" t="n">
         <v>1</v>
@@ -11984,7 +11954,7 @@
         <v>13</v>
       </c>
       <c r="K118" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L118" t="n">
         <v>25</v>
@@ -12017,10 +11987,10 @@
         </is>
       </c>
       <c r="X118" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="Y118" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="Z118" t="n">
         <v>0.86</v>
@@ -12032,7 +12002,7 @@
         <v>3</v>
       </c>
       <c r="AC118" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.7709999999999999</v>
       </c>
       <c r="AD118" t="n">
         <v>1</v>
@@ -12085,7 +12055,7 @@
         <v>13</v>
       </c>
       <c r="L119" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
@@ -12124,13 +12094,13 @@
         <v>0.67</v>
       </c>
       <c r="AA119" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="AB119" t="n">
         <v>2</v>
       </c>
       <c r="AC119" t="n">
-        <v>0.8865000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="AD119" t="n">
         <v>1</v>
@@ -12183,7 +12153,7 @@
         <v>13</v>
       </c>
       <c r="L120" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
@@ -12222,13 +12192,13 @@
         <v>1</v>
       </c>
       <c r="AA120" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="AB120" t="n">
         <v>1</v>
       </c>
       <c r="AC120" t="n">
-        <v>0.9164999999999999</v>
+        <v>0.9089999999999999</v>
       </c>
       <c r="AD120" t="n">
         <v>1</v>
@@ -12281,7 +12251,7 @@
         <v>13</v>
       </c>
       <c r="L121" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
@@ -12320,13 +12290,13 @@
         <v>0.67</v>
       </c>
       <c r="AA121" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
       <c r="AB121" t="n">
         <v>3</v>
       </c>
       <c r="AC121" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8075</v>
       </c>
       <c r="AD121" t="n">
         <v>1</v>
@@ -12964,7 +12934,7 @@
         <v>14</v>
       </c>
       <c r="K128" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="L128" t="n">
         <v>25</v>
@@ -12975,7 +12945,7 @@
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>unoccupied_8</t>
+          <t>unoccupied_12</t>
         </is>
       </c>
       <c r="R128" t="inlineStr"/>
@@ -12997,10 +12967,10 @@
         </is>
       </c>
       <c r="X128" t="n">
-        <v>0.57</v>
+        <v>0.61</v>
       </c>
       <c r="Y128" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="Z128" t="n">
         <v>0.86</v>
@@ -13009,10 +12979,10 @@
         <v>0.79</v>
       </c>
       <c r="AB128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC128" t="n">
-        <v>0.6575</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="AD128" t="n">
         <v>1</v>
@@ -13062,7 +13032,7 @@
         <v>14</v>
       </c>
       <c r="K129" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="L129" t="n">
         <v>25</v>
@@ -13073,7 +13043,7 @@
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>unoccupied_8</t>
+          <t>unoccupied_12</t>
         </is>
       </c>
       <c r="R129" t="inlineStr"/>
@@ -13095,10 +13065,10 @@
         </is>
       </c>
       <c r="X129" t="n">
-        <v>0.66</v>
+        <v>0.7</v>
       </c>
       <c r="Y129" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z129" t="n">
         <v>0.15</v>
@@ -13110,7 +13080,7 @@
         <v>3</v>
       </c>
       <c r="AC129" t="n">
-        <v>0.5325</v>
+        <v>0.5549999999999999</v>
       </c>
       <c r="AD129" t="n">
         <v>1</v>
@@ -13160,7 +13130,7 @@
         <v>14</v>
       </c>
       <c r="K130" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="L130" t="n">
         <v>25</v>
@@ -13171,7 +13141,7 @@
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>unoccupied_8</t>
+          <t>unoccupied_12</t>
         </is>
       </c>
       <c r="R130" t="inlineStr"/>
@@ -13205,7 +13175,7 @@
         <v>0.15</v>
       </c>
       <c r="AB130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC130" t="n">
         <v>0.6724999999999999</v>
@@ -13255,13 +13225,13 @@
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
       <c r="J131" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K131" t="n">
         <v>13</v>
       </c>
       <c r="L131" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
@@ -13269,7 +13239,7 @@
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>unoccupied_16</t>
+          <t>unoccupied_18</t>
         </is>
       </c>
       <c r="R131" t="inlineStr"/>
@@ -13291,10 +13261,10 @@
         </is>
       </c>
       <c r="X131" t="n">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="Y131" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
       <c r="Z131" t="n">
         <v>0.86</v>
@@ -13306,7 +13276,7 @@
         <v>1</v>
       </c>
       <c r="AC131" t="n">
-        <v>0.7755000000000001</v>
+        <v>0.7985</v>
       </c>
       <c r="AD131" t="n">
         <v>1</v>
@@ -13353,13 +13323,13 @@
       <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr"/>
       <c r="J132" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K132" t="n">
         <v>13</v>
       </c>
       <c r="L132" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
@@ -13367,7 +13337,7 @@
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>unoccupied_16</t>
+          <t>unoccupied_18</t>
         </is>
       </c>
       <c r="R132" t="inlineStr"/>
@@ -13389,10 +13359,10 @@
         </is>
       </c>
       <c r="X132" t="n">
-        <v>0.79</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y132" t="n">
-        <v>0.78</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z132" t="n">
         <v>0.15</v>
@@ -13404,7 +13374,7 @@
         <v>3</v>
       </c>
       <c r="AC132" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.636</v>
       </c>
       <c r="AD132" t="n">
         <v>1</v>
@@ -13451,13 +13421,13 @@
       <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="K133" t="n">
         <v>13</v>
       </c>
       <c r="L133" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
@@ -13465,7 +13435,7 @@
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>unoccupied_16</t>
+          <t>unoccupied_18</t>
         </is>
       </c>
       <c r="R133" t="inlineStr"/>
@@ -13549,7 +13519,7 @@
       <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K134" t="n">
         <v>13</v>
@@ -13585,10 +13555,10 @@
         </is>
       </c>
       <c r="X134" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="Y134" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="Z134" t="n">
         <v>0.76</v>
@@ -13600,7 +13570,7 @@
         <v>3</v>
       </c>
       <c r="AC134" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.6440000000000001</v>
       </c>
       <c r="AD134" t="n">
         <v>1</v>
@@ -13647,7 +13617,7 @@
       <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K135" t="n">
         <v>13</v>
@@ -13683,10 +13653,10 @@
         </is>
       </c>
       <c r="X135" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="Y135" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="Z135" t="n">
         <v>0.93</v>
@@ -13698,7 +13668,7 @@
         <v>1</v>
       </c>
       <c r="AC135" t="n">
-        <v>0.6970000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="AD135" t="n">
         <v>1</v>
@@ -13745,7 +13715,7 @@
       <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K136" t="n">
         <v>13</v>
@@ -13781,10 +13751,10 @@
         </is>
       </c>
       <c r="X136" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="Y136" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="Z136" t="n">
         <v>0.67</v>
@@ -13796,7 +13766,7 @@
         <v>2</v>
       </c>
       <c r="AC136" t="n">
-        <v>0.671</v>
+        <v>0.6775</v>
       </c>
       <c r="AD136" t="n">
         <v>1</v>
@@ -14137,10 +14107,10 @@
       <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr"/>
       <c r="J140" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K140" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L140" t="n">
         <v>25</v>
@@ -14173,10 +14143,10 @@
         </is>
       </c>
       <c r="X140" t="n">
-        <v>0.84</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Y140" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="Z140" t="n">
         <v>0.7</v>
@@ -14188,7 +14158,7 @@
         <v>2</v>
       </c>
       <c r="AC140" t="n">
-        <v>0.781</v>
+        <v>0.6869999999999999</v>
       </c>
       <c r="AD140" t="n">
         <v>1</v>
@@ -14235,10 +14205,10 @@
       <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr"/>
       <c r="J141" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K141" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L141" t="n">
         <v>25</v>
@@ -14271,10 +14241,10 @@
         </is>
       </c>
       <c r="X141" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="Y141" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.66</v>
       </c>
       <c r="Z141" t="n">
         <v>1</v>
@@ -14286,7 +14256,7 @@
         <v>1</v>
       </c>
       <c r="AC141" t="n">
-        <v>0.8150000000000001</v>
+        <v>0.7115</v>
       </c>
       <c r="AD141" t="n">
         <v>1</v>
@@ -14333,10 +14303,10 @@
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="K142" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L142" t="n">
         <v>25</v>
@@ -14369,10 +14339,10 @@
         </is>
       </c>
       <c r="X142" t="n">
-        <v>0.77</v>
+        <v>0.59</v>
       </c>
       <c r="Y142" t="n">
-        <v>0.79</v>
+        <v>0.62</v>
       </c>
       <c r="Z142" t="n">
         <v>0.78</v>
@@ -14384,7 +14354,7 @@
         <v>3</v>
       </c>
       <c r="AC142" t="n">
-        <v>0.755</v>
+        <v>0.6415000000000001</v>
       </c>
       <c r="AD142" t="n">
         <v>1</v>
@@ -14431,10 +14401,10 @@
       <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K143" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L143" t="n">
         <v>3</v>
@@ -14467,10 +14437,10 @@
         </is>
       </c>
       <c r="X143" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="Y143" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="Z143" t="n">
         <v>0.78</v>
@@ -14482,7 +14452,7 @@
         <v>2</v>
       </c>
       <c r="AC143" t="n">
-        <v>0.792</v>
+        <v>0.7205</v>
       </c>
       <c r="AD143" t="n">
         <v>1</v>
@@ -14529,10 +14499,10 @@
       <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K144" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L144" t="n">
         <v>3</v>
@@ -14565,10 +14535,10 @@
         </is>
       </c>
       <c r="X144" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="Y144" t="n">
-        <v>0.78</v>
+        <v>0.66</v>
       </c>
       <c r="Z144" t="n">
         <v>1</v>
@@ -14580,7 +14550,7 @@
         <v>1</v>
       </c>
       <c r="AC144" t="n">
-        <v>0.8164999999999999</v>
+        <v>0.7385</v>
       </c>
       <c r="AD144" t="n">
         <v>1</v>
@@ -14627,10 +14597,10 @@
       <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K145" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L145" t="n">
         <v>3</v>
@@ -14663,10 +14633,10 @@
         </is>
       </c>
       <c r="X145" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="Y145" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="Z145" t="n">
         <v>0.61</v>
@@ -14678,7 +14648,7 @@
         <v>3</v>
       </c>
       <c r="AC145" t="n">
-        <v>0.6995</v>
+        <v>0.615</v>
       </c>
       <c r="AD145" t="n">
         <v>1</v>
@@ -14725,7 +14695,7 @@
       <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr"/>
       <c r="J146" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K146" t="n">
         <v>14</v>
@@ -14761,10 +14731,10 @@
         </is>
       </c>
       <c r="X146" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="Y146" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="Z146" t="n">
         <v>0.7</v>
@@ -14773,10 +14743,10 @@
         <v>0.73</v>
       </c>
       <c r="AB146" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC146" t="n">
-        <v>0.8510000000000001</v>
+        <v>0.8995</v>
       </c>
       <c r="AD146" t="n">
         <v>1</v>
@@ -14823,7 +14793,7 @@
       <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr"/>
       <c r="J147" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K147" t="n">
         <v>14</v>
@@ -14859,10 +14829,10 @@
         </is>
       </c>
       <c r="X147" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="Y147" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="Z147" t="n">
         <v>0.93</v>
@@ -14874,7 +14844,7 @@
         <v>1</v>
       </c>
       <c r="AC147" t="n">
-        <v>0.8775000000000002</v>
+        <v>0.9455</v>
       </c>
       <c r="AD147" t="n">
         <v>1</v>
@@ -14921,7 +14891,7 @@
       <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="J148" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K148" t="n">
         <v>14</v>
@@ -14957,10 +14927,10 @@
         </is>
       </c>
       <c r="X148" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="Y148" t="n">
-        <v>0.87</v>
+        <v>0.98</v>
       </c>
       <c r="Z148" t="n">
         <v>0.78</v>
@@ -14969,10 +14939,10 @@
         <v>0.73</v>
       </c>
       <c r="AB148" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC148" t="n">
-        <v>0.8280000000000001</v>
+        <v>0.9025000000000001</v>
       </c>
       <c r="AD148" t="n">
         <v>1</v>
@@ -15025,7 +14995,7 @@
         <v>13</v>
       </c>
       <c r="L149" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
@@ -15064,13 +15034,13 @@
         <v>0.45</v>
       </c>
       <c r="AA149" t="n">
-        <v>0.72</v>
+        <v>0.66</v>
       </c>
       <c r="AB149" t="n">
         <v>3</v>
       </c>
       <c r="AC149" t="n">
-        <v>0.348</v>
+        <v>0.339</v>
       </c>
       <c r="AD149" t="n">
         <v>1</v>
@@ -15123,7 +15093,7 @@
         <v>13</v>
       </c>
       <c r="L150" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
@@ -15162,13 +15132,13 @@
         <v>0.93</v>
       </c>
       <c r="AA150" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AB150" t="n">
         <v>2</v>
       </c>
       <c r="AC150" t="n">
-        <v>0.5185</v>
+        <v>0.5095000000000001</v>
       </c>
       <c r="AD150" t="n">
         <v>1</v>
@@ -15221,7 +15191,7 @@
         <v>13</v>
       </c>
       <c r="L151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
@@ -15260,13 +15230,13 @@
         <v>0.67</v>
       </c>
       <c r="AA151" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AB151" t="n">
         <v>1</v>
       </c>
       <c r="AC151" t="n">
-        <v>0.522</v>
+        <v>0.5129999999999999</v>
       </c>
       <c r="AD151" t="n">
         <v>1</v>
@@ -15610,7 +15580,7 @@
         <v>13</v>
       </c>
       <c r="K155" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L155" t="n">
         <v>13</v>
@@ -15708,7 +15678,7 @@
         <v>13</v>
       </c>
       <c r="K156" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L156" t="n">
         <v>13</v>
@@ -15806,7 +15776,7 @@
         <v>13</v>
       </c>
       <c r="K157" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L157" t="n">
         <v>13</v>
@@ -15851,7 +15821,7 @@
         <v>0.87</v>
       </c>
       <c r="AB157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC157" t="n">
         <v>0.9524999999999999</v>
@@ -16195,7 +16165,7 @@
       <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="J161" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K161" t="n">
         <v>13</v>
@@ -16293,7 +16263,7 @@
       <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr"/>
       <c r="J162" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K162" t="n">
         <v>13</v>
@@ -16341,7 +16311,7 @@
         <v>0.72</v>
       </c>
       <c r="AB162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC162" t="n">
         <v>0.9279999999999999</v>
@@ -16391,7 +16361,7 @@
       <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K163" t="n">
         <v>13</v>
@@ -16427,10 +16397,10 @@
         </is>
       </c>
       <c r="X163" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="Y163" t="n">
-        <v>0.97</v>
+        <v>0.99</v>
       </c>
       <c r="Z163" t="n">
         <v>0.93</v>
@@ -16439,10 +16409,10 @@
         <v>0.72</v>
       </c>
       <c r="AB163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC163" t="n">
-        <v>0.9275</v>
+        <v>0.9375</v>
       </c>
       <c r="AD163" t="n">
         <v>1</v>
@@ -16489,7 +16459,7 @@
       <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K164" t="n">
         <v>13</v>
@@ -16587,7 +16557,7 @@
       <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr"/>
       <c r="J165" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K165" t="n">
         <v>13</v>
@@ -16685,7 +16655,7 @@
       <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K166" t="n">
         <v>13</v>
@@ -16786,7 +16756,7 @@
         <v>20</v>
       </c>
       <c r="K167" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L167" t="n">
         <v>18</v>
@@ -16819,10 +16789,10 @@
         </is>
       </c>
       <c r="X167" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="Y167" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="Z167" t="n">
         <v>0.7</v>
@@ -16834,7 +16804,7 @@
         <v>3</v>
       </c>
       <c r="AC167" t="n">
-        <v>0.833</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="AD167" t="n">
         <v>1</v>
@@ -16884,7 +16854,7 @@
         <v>20</v>
       </c>
       <c r="K168" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L168" t="n">
         <v>18</v>
@@ -16917,10 +16887,10 @@
         </is>
       </c>
       <c r="X168" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="Y168" t="n">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="Z168" t="n">
         <v>1</v>
@@ -16932,7 +16902,7 @@
         <v>2</v>
       </c>
       <c r="AC168" t="n">
-        <v>0.9059999999999999</v>
+        <v>0.893</v>
       </c>
       <c r="AD168" t="n">
         <v>1</v>
@@ -16982,7 +16952,7 @@
         <v>20</v>
       </c>
       <c r="K169" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L169" t="n">
         <v>18</v>
@@ -17077,7 +17047,7 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K170" t="n">
         <v>13</v>
@@ -17113,10 +17083,10 @@
         </is>
       </c>
       <c r="X170" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="Y170" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="Z170" t="n">
         <v>0.67</v>
@@ -17128,7 +17098,7 @@
         <v>3</v>
       </c>
       <c r="AC170" t="n">
-        <v>0.5565</v>
+        <v>0.5825</v>
       </c>
       <c r="AD170" t="n">
         <v>1</v>
@@ -17175,7 +17145,7 @@
       <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="J171" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K171" t="n">
         <v>13</v>
@@ -17211,10 +17181,10 @@
         </is>
       </c>
       <c r="X171" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="Y171" t="n">
-        <v>0.51</v>
+        <v>0.54</v>
       </c>
       <c r="Z171" t="n">
         <v>1</v>
@@ -17226,7 +17196,7 @@
         <v>1</v>
       </c>
       <c r="AC171" t="n">
-        <v>0.6485</v>
+        <v>0.6709999999999999</v>
       </c>
       <c r="AD171" t="n">
         <v>1</v>
@@ -17273,7 +17243,7 @@
       <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr"/>
       <c r="J172" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K172" t="n">
         <v>13</v>
@@ -17309,10 +17279,10 @@
         </is>
       </c>
       <c r="X172" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="Y172" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="Z172" t="n">
         <v>0.67</v>
@@ -17324,7 +17294,7 @@
         <v>2</v>
       </c>
       <c r="AC172" t="n">
-        <v>0.6154999999999999</v>
+        <v>0.6385000000000001</v>
       </c>
       <c r="AD172" t="n">
         <v>1</v>
@@ -17371,13 +17341,13 @@
       <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr"/>
       <c r="J173" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K173" t="n">
         <v>13</v>
       </c>
       <c r="L173" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M173" t="inlineStr"/>
       <c r="N173" t="inlineStr"/>
@@ -17407,22 +17377,22 @@
         </is>
       </c>
       <c r="X173" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="Y173" t="n">
-        <v>0.55</v>
+        <v>0.34</v>
       </c>
       <c r="Z173" t="n">
         <v>0.73</v>
       </c>
       <c r="AA173" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="AB173" t="n">
         <v>3</v>
       </c>
       <c r="AC173" t="n">
-        <v>0.619</v>
+        <v>0.4795</v>
       </c>
       <c r="AD173" t="n">
         <v>1</v>
@@ -17469,13 +17439,13 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K174" t="n">
         <v>13</v>
       </c>
       <c r="L174" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
@@ -17505,22 +17475,22 @@
         </is>
       </c>
       <c r="X174" t="n">
-        <v>0.58</v>
+        <v>0.42</v>
       </c>
       <c r="Y174" t="n">
-        <v>0.59</v>
+        <v>0.43</v>
       </c>
       <c r="Z174" t="n">
         <v>0.92</v>
       </c>
       <c r="AA174" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="AB174" t="n">
         <v>1</v>
       </c>
       <c r="AC174" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.585</v>
       </c>
       <c r="AD174" t="n">
         <v>1</v>
@@ -17567,13 +17537,13 @@
       <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr"/>
       <c r="J175" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K175" t="n">
         <v>13</v>
       </c>
       <c r="L175" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M175" t="inlineStr"/>
       <c r="N175" t="inlineStr"/>
@@ -17603,22 +17573,22 @@
         </is>
       </c>
       <c r="X175" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="Y175" t="n">
-        <v>0.63</v>
+        <v>0.52</v>
       </c>
       <c r="Z175" t="n">
         <v>0.51</v>
       </c>
       <c r="AA175" t="n">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="AB175" t="n">
         <v>2</v>
       </c>
       <c r="AC175" t="n">
-        <v>0.6345</v>
+        <v>0.5705</v>
       </c>
       <c r="AD175" t="n">
         <v>1</v>
@@ -17671,7 +17641,7 @@
         <v>13</v>
       </c>
       <c r="L176" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
@@ -17710,13 +17680,13 @@
         <v>0.29</v>
       </c>
       <c r="AA176" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB176" t="n">
         <v>3</v>
       </c>
       <c r="AC176" t="n">
-        <v>0.6599999999999999</v>
+        <v>0.6554999999999999</v>
       </c>
       <c r="AD176" t="n">
         <v>1</v>
@@ -17769,7 +17739,7 @@
         <v>13</v>
       </c>
       <c r="L177" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
@@ -17808,13 +17778,13 @@
         <v>0.7</v>
       </c>
       <c r="AA177" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB177" t="n">
         <v>2</v>
       </c>
       <c r="AC177" t="n">
-        <v>0.7045</v>
+        <v>0.6985</v>
       </c>
       <c r="AD177" t="n">
         <v>1</v>
@@ -17867,7 +17837,7 @@
         <v>13</v>
       </c>
       <c r="L178" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
@@ -17906,13 +17876,13 @@
         <v>0.93</v>
       </c>
       <c r="AA178" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AB178" t="n">
         <v>1</v>
       </c>
       <c r="AC178" t="n">
-        <v>0.7244999999999999</v>
+        <v>0.7184999999999999</v>
       </c>
       <c r="AD178" t="n">
         <v>1</v>
@@ -17959,13 +17929,13 @@
       <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr"/>
       <c r="J179" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K179" t="n">
         <v>13</v>
       </c>
       <c r="L179" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
@@ -18004,13 +17974,13 @@
         <v>0.7</v>
       </c>
       <c r="AA179" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AB179" t="n">
         <v>3</v>
       </c>
       <c r="AC179" t="n">
-        <v>0.8875</v>
+        <v>0.8889999999999999</v>
       </c>
       <c r="AD179" t="n">
         <v>1</v>
@@ -18057,13 +18027,13 @@
       <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr"/>
       <c r="J180" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K180" t="n">
         <v>13</v>
       </c>
       <c r="L180" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M180" t="inlineStr"/>
       <c r="N180" t="inlineStr"/>
@@ -18102,13 +18072,13 @@
         <v>0.93</v>
       </c>
       <c r="AA180" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AB180" t="n">
         <v>1</v>
       </c>
       <c r="AC180" t="n">
-        <v>0.9335</v>
+        <v>0.9349999999999999</v>
       </c>
       <c r="AD180" t="n">
         <v>1</v>
@@ -18155,13 +18125,13 @@
       <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr"/>
       <c r="J181" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K181" t="n">
         <v>13</v>
       </c>
       <c r="L181" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
@@ -18194,19 +18164,19 @@
         <v>1</v>
       </c>
       <c r="Y181" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="Z181" t="n">
         <v>0.86</v>
       </c>
       <c r="AA181" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="AB181" t="n">
         <v>2</v>
       </c>
       <c r="AC181" t="n">
-        <v>0.9195</v>
+        <v>0.9175</v>
       </c>
       <c r="AD181" t="n">
         <v>1</v>
@@ -18847,7 +18817,7 @@
         <v>13</v>
       </c>
       <c r="L188" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M188" t="inlineStr"/>
       <c r="N188" t="inlineStr"/>
@@ -18945,7 +18915,7 @@
         <v>13</v>
       </c>
       <c r="L189" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
@@ -18984,13 +18954,13 @@
         <v>0.15</v>
       </c>
       <c r="AA189" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="AB189" t="n">
         <v>2</v>
       </c>
       <c r="AC189" t="n">
-        <v>0.6359999999999999</v>
+        <v>0.6375</v>
       </c>
       <c r="AD189" t="n">
         <v>1</v>
@@ -19043,7 +19013,7 @@
         <v>13</v>
       </c>
       <c r="L190" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
@@ -19082,13 +19052,13 @@
         <v>0.51</v>
       </c>
       <c r="AA190" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="AB190" t="n">
         <v>1</v>
       </c>
       <c r="AC190" t="n">
-        <v>0.7219999999999999</v>
+        <v>0.7249999999999999</v>
       </c>
       <c r="AD190" t="n">
         <v>1</v>
@@ -20020,7 +19990,7 @@
         <v>13</v>
       </c>
       <c r="K200" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L200" t="n">
         <v>25</v>
@@ -20031,7 +20001,7 @@
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="R200" t="inlineStr"/>
@@ -20053,10 +20023,10 @@
         </is>
       </c>
       <c r="X200" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="Y200" t="n">
-        <v>0.76</v>
+        <v>0.83</v>
       </c>
       <c r="Z200" t="n">
         <v>0</v>
@@ -20068,7 +20038,7 @@
         <v>3</v>
       </c>
       <c r="AC200" t="n">
-        <v>0.5375</v>
+        <v>0.586</v>
       </c>
       <c r="AD200" t="n">
         <v>1</v>
@@ -20118,7 +20088,7 @@
         <v>13</v>
       </c>
       <c r="K201" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L201" t="n">
         <v>25</v>
@@ -20129,7 +20099,7 @@
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="R201" t="inlineStr"/>
@@ -20151,10 +20121,10 @@
         </is>
       </c>
       <c r="X201" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="Y201" t="n">
-        <v>0.72</v>
+        <v>0.8</v>
       </c>
       <c r="Z201" t="n">
         <v>0.41</v>
@@ -20166,7 +20136,7 @@
         <v>2</v>
       </c>
       <c r="AC201" t="n">
-        <v>0.6415</v>
+        <v>0.6935</v>
       </c>
       <c r="AD201" t="n">
         <v>1</v>
@@ -20216,7 +20186,7 @@
         <v>13</v>
       </c>
       <c r="K202" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L202" t="n">
         <v>25</v>
@@ -20227,7 +20197,7 @@
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr">
         <is>
-          <t>unoccupied_3</t>
+          <t>unoccupied_4</t>
         </is>
       </c>
       <c r="R202" t="inlineStr"/>
@@ -20249,10 +20219,10 @@
         </is>
       </c>
       <c r="X202" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="Y202" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="Z202" t="n">
         <v>0.7</v>
@@ -20264,7 +20234,7 @@
         <v>1</v>
       </c>
       <c r="AC202" t="n">
-        <v>0.67</v>
+        <v>0.7284999999999999</v>
       </c>
       <c r="AD202" t="n">
         <v>1</v>
@@ -20605,7 +20575,7 @@
       <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr"/>
       <c r="J206" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K206" t="n">
         <v>13</v>
@@ -20641,10 +20611,10 @@
         </is>
       </c>
       <c r="X206" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
       <c r="Y206" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="Z206" t="n">
         <v>0.78</v>
@@ -20656,7 +20626,7 @@
         <v>3</v>
       </c>
       <c r="AC206" t="n">
-        <v>0.6365000000000001</v>
+        <v>0.659</v>
       </c>
       <c r="AD206" t="n">
         <v>1</v>
@@ -20703,7 +20673,7 @@
       <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr"/>
       <c r="J207" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K207" t="n">
         <v>13</v>
@@ -20739,10 +20709,10 @@
         </is>
       </c>
       <c r="X207" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="Y207" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="Z207" t="n">
         <v>1</v>
@@ -20754,7 +20724,7 @@
         <v>1</v>
       </c>
       <c r="AC207" t="n">
-        <v>0.7000000000000001</v>
+        <v>0.7194999999999999</v>
       </c>
       <c r="AD207" t="n">
         <v>1</v>
@@ -20801,7 +20771,7 @@
       <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr"/>
       <c r="J208" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K208" t="n">
         <v>13</v>
@@ -20837,10 +20807,10 @@
         </is>
       </c>
       <c r="X208" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
       <c r="Y208" t="n">
-        <v>0.61</v>
+        <v>0.64</v>
       </c>
       <c r="Z208" t="n">
         <v>0.78</v>
@@ -20852,7 +20822,7 @@
         <v>2</v>
       </c>
       <c r="AC208" t="n">
-        <v>0.6785</v>
+        <v>0.695</v>
       </c>
       <c r="AD208" t="n">
         <v>1</v>
@@ -21198,7 +21168,7 @@
       <c r="K212" t="inlineStr"/>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
@@ -21231,10 +21201,10 @@
         </is>
       </c>
       <c r="X212" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="Y212" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="Z212" t="n">
         <v>1</v>
@@ -21246,7 +21216,7 @@
         <v>1</v>
       </c>
       <c r="AC212" t="n">
-        <v>0.6735000000000001</v>
+        <v>0.5815</v>
       </c>
       <c r="AD212" t="n">
         <v>1</v>
@@ -21298,7 +21268,7 @@
       <c r="K213" t="inlineStr"/>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
@@ -21331,10 +21301,10 @@
         </is>
       </c>
       <c r="X213" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="Y213" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="Z213" t="n">
         <v>0.34</v>
@@ -21346,7 +21316,7 @@
         <v>3</v>
       </c>
       <c r="AC213" t="n">
-        <v>0.5415</v>
+        <v>0.4745</v>
       </c>
       <c r="AD213" t="n">
         <v>1</v>
@@ -21398,7 +21368,7 @@
       <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
@@ -21431,10 +21401,10 @@
         </is>
       </c>
       <c r="X214" t="n">
-        <v>0.78</v>
+        <v>0.72</v>
       </c>
       <c r="Y214" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="Z214" t="n">
         <v>0.64</v>
@@ -21446,7 +21416,7 @@
         <v>2</v>
       </c>
       <c r="AC214" t="n">
-        <v>0.6014999999999999</v>
+        <v>0.5275</v>
       </c>
       <c r="AD214" t="n">
         <v>1</v>
@@ -21511,7 +21481,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="T215" t="inlineStr">
@@ -21611,7 +21581,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
@@ -21711,7 +21681,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
@@ -21798,7 +21768,7 @@
       <c r="K218" t="inlineStr"/>
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
@@ -21831,10 +21801,10 @@
         </is>
       </c>
       <c r="X218" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="Y218" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="Z218" t="n">
         <v>1</v>
@@ -21846,7 +21816,7 @@
         <v>1</v>
       </c>
       <c r="AC218" t="n">
-        <v>0.792</v>
+        <v>0.819</v>
       </c>
       <c r="AD218" t="n">
         <v>1</v>
@@ -21898,7 +21868,7 @@
       <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
@@ -21931,10 +21901,10 @@
         </is>
       </c>
       <c r="X219" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
       <c r="Y219" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="Z219" t="n">
         <v>0.57</v>
@@ -21946,7 +21916,7 @@
         <v>3</v>
       </c>
       <c r="AC219" t="n">
-        <v>0.5545</v>
+        <v>0.5905</v>
       </c>
       <c r="AD219" t="n">
         <v>1</v>
@@ -21998,7 +21968,7 @@
       <c r="K220" t="inlineStr"/>
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
@@ -22031,10 +22001,10 @@
         </is>
       </c>
       <c r="X220" t="n">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="Y220" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="Z220" t="n">
         <v>0.57</v>
@@ -22046,7 +22016,7 @@
         <v>2</v>
       </c>
       <c r="AC220" t="n">
-        <v>0.6174999999999999</v>
+        <v>0.6445</v>
       </c>
       <c r="AD220" t="n">
         <v>1</v>
@@ -22098,7 +22068,7 @@
       <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
@@ -22131,10 +22101,10 @@
         </is>
       </c>
       <c r="X221" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="Y221" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="Z221" t="n">
         <v>1</v>
@@ -22146,7 +22116,7 @@
         <v>1</v>
       </c>
       <c r="AC221" t="n">
-        <v>0.7785000000000001</v>
+        <v>0.8055</v>
       </c>
       <c r="AD221" t="n">
         <v>1</v>
@@ -22198,7 +22168,7 @@
       <c r="K222" t="inlineStr"/>
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
@@ -22231,10 +22201,10 @@
         </is>
       </c>
       <c r="X222" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="Y222" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="Z222" t="n">
         <v>0.23</v>
@@ -22246,7 +22216,7 @@
         <v>3</v>
       </c>
       <c r="AC222" t="n">
-        <v>0.497</v>
+        <v>0.5239999999999999</v>
       </c>
       <c r="AD222" t="n">
         <v>1</v>
@@ -22298,7 +22268,7 @@
       <c r="K223" t="inlineStr"/>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
@@ -22331,10 +22301,10 @@
         </is>
       </c>
       <c r="X223" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="Y223" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="Z223" t="n">
         <v>0.79</v>
@@ -22346,7 +22316,7 @@
         <v>2</v>
       </c>
       <c r="AC223" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6555</v>
       </c>
       <c r="AD223" t="n">
         <v>1</v>
@@ -22398,7 +22368,7 @@
       <c r="K224" t="inlineStr"/>
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
@@ -22431,10 +22401,10 @@
         </is>
       </c>
       <c r="X224" t="n">
-        <v>0.46</v>
+        <v>0.59</v>
       </c>
       <c r="Y224" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z224" t="n">
         <v>0.52</v>
@@ -22446,7 +22416,7 @@
         <v>2</v>
       </c>
       <c r="AC224" t="n">
-        <v>0.32</v>
+        <v>0.3835</v>
       </c>
       <c r="AD224" t="n">
         <v>1</v>
@@ -22498,7 +22468,7 @@
       <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N225" t="inlineStr"/>
       <c r="O225" t="inlineStr"/>
@@ -22531,7 +22501,7 @@
         </is>
       </c>
       <c r="X225" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="Y225" t="n">
         <v>0</v>
@@ -22546,7 +22516,7 @@
         <v>3</v>
       </c>
       <c r="AC225" t="n">
-        <v>0.289</v>
+        <v>0.337</v>
       </c>
       <c r="AD225" t="n">
         <v>1</v>
@@ -22598,7 +22568,7 @@
       <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N226" t="inlineStr"/>
       <c r="O226" t="inlineStr"/>
@@ -22631,7 +22601,7 @@
         </is>
       </c>
       <c r="X226" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="Y226" t="n">
         <v>0</v>
@@ -22646,7 +22616,7 @@
         <v>1</v>
       </c>
       <c r="AC226" t="n">
-        <v>0.35</v>
+        <v>0.398</v>
       </c>
       <c r="AD226" t="n">
         <v>1</v>
@@ -22998,7 +22968,7 @@
       <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N230" t="inlineStr"/>
       <c r="O230" t="inlineStr"/>
@@ -23031,7 +23001,7 @@
         </is>
       </c>
       <c r="X230" t="n">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="Y230" t="n">
         <v>0</v>
@@ -23046,7 +23016,7 @@
         <v>2</v>
       </c>
       <c r="AC230" t="n">
-        <v>0.2705</v>
+        <v>0.2525</v>
       </c>
       <c r="AD230" t="n">
         <v>1</v>
@@ -23098,7 +23068,7 @@
       <c r="K231" t="inlineStr"/>
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N231" t="inlineStr"/>
       <c r="O231" t="inlineStr"/>
@@ -23131,7 +23101,7 @@
         </is>
       </c>
       <c r="X231" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Y231" t="n">
         <v>0</v>
@@ -23146,7 +23116,7 @@
         <v>1</v>
       </c>
       <c r="AC231" t="n">
-        <v>0.359</v>
+        <v>0.35</v>
       </c>
       <c r="AD231" t="n">
         <v>1</v>
@@ -23198,7 +23168,7 @@
       <c r="K232" t="inlineStr"/>
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N232" t="inlineStr"/>
       <c r="O232" t="inlineStr"/>
@@ -23231,7 +23201,7 @@
         </is>
       </c>
       <c r="X232" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="Y232" t="n">
         <v>0</v>
@@ -23246,7 +23216,7 @@
         <v>3</v>
       </c>
       <c r="AC232" t="n">
-        <v>0.245</v>
+        <v>0.236</v>
       </c>
       <c r="AD232" t="n">
         <v>1</v>
@@ -23298,7 +23268,7 @@
       <c r="K233" t="inlineStr"/>
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N233" t="inlineStr"/>
       <c r="O233" t="inlineStr"/>
@@ -23331,10 +23301,10 @@
         </is>
       </c>
       <c r="X233" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="Y233" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="Z233" t="n">
         <v>0.57</v>
@@ -23346,7 +23316,7 @@
         <v>3</v>
       </c>
       <c r="AC233" t="n">
-        <v>0.5545</v>
+        <v>0.6309999999999999</v>
       </c>
       <c r="AD233" t="n">
         <v>1</v>
@@ -23398,7 +23368,7 @@
       <c r="K234" t="inlineStr"/>
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N234" t="inlineStr"/>
       <c r="O234" t="inlineStr"/>
@@ -23431,10 +23401,10 @@
         </is>
       </c>
       <c r="X234" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="Y234" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="Z234" t="n">
         <v>1</v>
@@ -23446,7 +23416,7 @@
         <v>1</v>
       </c>
       <c r="AC234" t="n">
-        <v>0.6465</v>
+        <v>0.7440000000000001</v>
       </c>
       <c r="AD234" t="n">
         <v>1</v>
@@ -23498,7 +23468,7 @@
       <c r="K235" t="inlineStr"/>
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N235" t="inlineStr"/>
       <c r="O235" t="inlineStr"/>
@@ -23531,10 +23501,10 @@
         </is>
       </c>
       <c r="X235" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="Y235" t="n">
-        <v>0.47</v>
+        <v>0.62</v>
       </c>
       <c r="Z235" t="n">
         <v>0.95</v>
@@ -23546,7 +23516,7 @@
         <v>2</v>
       </c>
       <c r="AC235" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.7220000000000001</v>
       </c>
       <c r="AD235" t="n">
         <v>1</v>
@@ -23598,7 +23568,7 @@
       <c r="K236" t="inlineStr"/>
       <c r="L236" t="inlineStr"/>
       <c r="M236" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N236" t="inlineStr"/>
       <c r="O236" t="inlineStr"/>
@@ -23631,10 +23601,10 @@
         </is>
       </c>
       <c r="X236" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="Y236" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z236" t="n">
         <v>0.29</v>
@@ -23646,7 +23616,7 @@
         <v>3</v>
       </c>
       <c r="AC236" t="n">
-        <v>0.3164999999999999</v>
+        <v>0.268</v>
       </c>
       <c r="AD236" t="n">
         <v>1</v>
@@ -23698,7 +23668,7 @@
       <c r="K237" t="inlineStr"/>
       <c r="L237" t="inlineStr"/>
       <c r="M237" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N237" t="inlineStr"/>
       <c r="O237" t="inlineStr"/>
@@ -23798,7 +23768,7 @@
       <c r="K238" t="inlineStr"/>
       <c r="L238" t="inlineStr"/>
       <c r="M238" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N238" t="inlineStr"/>
       <c r="O238" t="inlineStr"/>
@@ -23831,7 +23801,7 @@
         </is>
       </c>
       <c r="X238" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="Y238" t="n">
         <v>0</v>
@@ -23846,7 +23816,7 @@
         <v>1</v>
       </c>
       <c r="AC238" t="n">
-        <v>0.4309999999999999</v>
+        <v>0.4069999999999999</v>
       </c>
       <c r="AD238" t="n">
         <v>1</v>
@@ -24498,7 +24468,7 @@
       <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr"/>
       <c r="M245" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="N245" t="inlineStr"/>
       <c r="O245" t="inlineStr"/>
@@ -24531,10 +24501,10 @@
         </is>
       </c>
       <c r="X245" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="Y245" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="Z245" t="n">
         <v>0.26</v>
@@ -24546,7 +24516,7 @@
         <v>2</v>
       </c>
       <c r="AC245" t="n">
-        <v>0.5765</v>
+        <v>0.4349999999999999</v>
       </c>
       <c r="AD245" t="n">
         <v>1</v>
@@ -24598,7 +24568,7 @@
       <c r="K246" t="inlineStr"/>
       <c r="L246" t="inlineStr"/>
       <c r="M246" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="N246" t="inlineStr"/>
       <c r="O246" t="inlineStr"/>
@@ -24631,10 +24601,10 @@
         </is>
       </c>
       <c r="X246" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="Y246" t="n">
-        <v>0.65</v>
+        <v>0.36</v>
       </c>
       <c r="Z246" t="n">
         <v>0.09</v>
@@ -24646,7 +24616,7 @@
         <v>3</v>
       </c>
       <c r="AC246" t="n">
-        <v>0.5289999999999999</v>
+        <v>0.3945</v>
       </c>
       <c r="AD246" t="n">
         <v>1</v>
@@ -24698,7 +24668,7 @@
       <c r="K247" t="inlineStr"/>
       <c r="L247" t="inlineStr"/>
       <c r="M247" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="N247" t="inlineStr"/>
       <c r="O247" t="inlineStr"/>
@@ -24731,10 +24701,10 @@
         </is>
       </c>
       <c r="X247" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>0.62</v>
+        <v>0.31</v>
       </c>
       <c r="Z247" t="n">
         <v>1</v>
@@ -24746,7 +24716,7 @@
         <v>1</v>
       </c>
       <c r="AC247" t="n">
-        <v>0.669</v>
+        <v>0.4585</v>
       </c>
       <c r="AD247" t="n">
         <v>1</v>
@@ -24798,7 +24768,7 @@
       <c r="K248" t="inlineStr"/>
       <c r="L248" t="inlineStr"/>
       <c r="M248" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N248" t="inlineStr"/>
       <c r="O248" t="inlineStr"/>
@@ -24831,10 +24801,10 @@
         </is>
       </c>
       <c r="X248" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="Y248" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z248" t="n">
         <v>0.7</v>
@@ -24846,7 +24816,7 @@
         <v>2</v>
       </c>
       <c r="AC248" t="n">
-        <v>0.4279999999999999</v>
+        <v>0.4705</v>
       </c>
       <c r="AD248" t="n">
         <v>1</v>
@@ -24898,7 +24868,7 @@
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr"/>
       <c r="M249" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N249" t="inlineStr"/>
       <c r="O249" t="inlineStr"/>
@@ -24931,10 +24901,10 @@
         </is>
       </c>
       <c r="X249" t="n">
-        <v>0.59</v>
+        <v>0.65</v>
       </c>
       <c r="Y249" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z249" t="n">
         <v>0.83</v>
@@ -24946,7 +24916,7 @@
         <v>1</v>
       </c>
       <c r="AC249" t="n">
-        <v>0.4705</v>
+        <v>0.513</v>
       </c>
       <c r="AD249" t="n">
         <v>1</v>
@@ -24998,7 +24968,7 @@
       <c r="K250" t="inlineStr"/>
       <c r="L250" t="inlineStr"/>
       <c r="M250" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N250" t="inlineStr"/>
       <c r="O250" t="inlineStr"/>
@@ -25098,7 +25068,7 @@
       <c r="K251" t="inlineStr"/>
       <c r="L251" t="inlineStr"/>
       <c r="M251" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N251" t="inlineStr"/>
       <c r="O251" t="inlineStr"/>
@@ -25131,10 +25101,10 @@
         </is>
       </c>
       <c r="X251" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="Y251" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="Z251" t="n">
         <v>0.31</v>
@@ -25146,7 +25116,7 @@
         <v>3</v>
       </c>
       <c r="AC251" t="n">
-        <v>0.2795</v>
+        <v>0.38</v>
       </c>
       <c r="AD251" t="n">
         <v>1</v>
@@ -25198,7 +25168,7 @@
       <c r="K252" t="inlineStr"/>
       <c r="L252" t="inlineStr"/>
       <c r="M252" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N252" t="inlineStr"/>
       <c r="O252" t="inlineStr"/>
@@ -25234,7 +25204,7 @@
         <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="Z252" t="n">
         <v>1</v>
@@ -25246,7 +25216,7 @@
         <v>2</v>
       </c>
       <c r="AC252" t="n">
-        <v>0.35</v>
+        <v>0.4025</v>
       </c>
       <c r="AD252" t="n">
         <v>1</v>
@@ -25298,7 +25268,7 @@
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N253" t="inlineStr"/>
       <c r="O253" t="inlineStr"/>
@@ -25331,10 +25301,10 @@
         </is>
       </c>
       <c r="X253" t="n">
-        <v>0.54</v>
+        <v>0.7</v>
       </c>
       <c r="Y253" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="Z253" t="n">
         <v>0.63</v>
@@ -25346,7 +25316,7 @@
         <v>1</v>
       </c>
       <c r="AC253" t="n">
-        <v>0.3615</v>
+        <v>0.462</v>
       </c>
       <c r="AD253" t="n">
         <v>1</v>
@@ -25398,7 +25368,7 @@
       <c r="K254" t="inlineStr"/>
       <c r="L254" t="inlineStr"/>
       <c r="M254" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N254" t="inlineStr"/>
       <c r="O254" t="inlineStr"/>
@@ -25431,10 +25401,10 @@
         </is>
       </c>
       <c r="X254" t="n">
-        <v>0.76</v>
+        <v>0.7</v>
       </c>
       <c r="Y254" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="Z254" t="n">
         <v>0.73</v>
@@ -25446,7 +25416,7 @@
         <v>2</v>
       </c>
       <c r="AC254" t="n">
-        <v>0.615</v>
+        <v>0.541</v>
       </c>
       <c r="AD254" t="n">
         <v>1</v>
@@ -25498,7 +25468,7 @@
       <c r="K255" t="inlineStr"/>
       <c r="L255" t="inlineStr"/>
       <c r="M255" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N255" t="inlineStr"/>
       <c r="O255" t="inlineStr"/>
@@ -25531,10 +25501,10 @@
         </is>
       </c>
       <c r="X255" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="Y255" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="Z255" t="n">
         <v>0.83</v>
@@ -25546,7 +25516,7 @@
         <v>3</v>
       </c>
       <c r="AC255" t="n">
-        <v>0.593</v>
+        <v>0.495</v>
       </c>
       <c r="AD255" t="n">
         <v>1</v>
@@ -25598,7 +25568,7 @@
       <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N256" t="inlineStr"/>
       <c r="O256" t="inlineStr"/>
@@ -25631,10 +25601,10 @@
         </is>
       </c>
       <c r="X256" t="n">
-        <v>0.5</v>
+        <v>0.36</v>
       </c>
       <c r="Y256" t="n">
-        <v>0.47</v>
+        <v>0.31</v>
       </c>
       <c r="Z256" t="n">
         <v>1</v>
@@ -25646,7 +25616,7 @@
         <v>1</v>
       </c>
       <c r="AC256" t="n">
-        <v>0.6645</v>
+        <v>0.5665</v>
       </c>
       <c r="AD256" t="n">
         <v>1</v>
@@ -25698,7 +25668,7 @@
       <c r="K257" t="inlineStr"/>
       <c r="L257" t="inlineStr"/>
       <c r="M257" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="N257" t="inlineStr"/>
       <c r="O257" t="inlineStr"/>
@@ -25711,7 +25681,7 @@
       </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>11:59 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="T257" t="inlineStr">
@@ -25731,10 +25701,10 @@
         </is>
       </c>
       <c r="X257" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="Y257" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.82</v>
       </c>
       <c r="Z257" t="n">
         <v>0.89</v>
@@ -25746,7 +25716,7 @@
         <v>1</v>
       </c>
       <c r="AC257" t="n">
-        <v>0.9285000000000001</v>
+        <v>0.8625</v>
       </c>
       <c r="AD257" t="n">
         <v>1</v>
@@ -25798,7 +25768,7 @@
       <c r="K258" t="inlineStr"/>
       <c r="L258" t="inlineStr"/>
       <c r="M258" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="N258" t="inlineStr"/>
       <c r="O258" t="inlineStr"/>
@@ -25811,7 +25781,7 @@
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>11:59 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="T258" t="inlineStr">
@@ -25831,10 +25801,10 @@
         </is>
       </c>
       <c r="X258" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="Y258" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z258" t="n">
         <v>0.52</v>
@@ -25846,7 +25816,7 @@
         <v>3</v>
       </c>
       <c r="AC258" t="n">
-        <v>0.7639999999999999</v>
+        <v>0.698</v>
       </c>
       <c r="AD258" t="n">
         <v>1</v>
@@ -25898,7 +25868,7 @@
       <c r="K259" t="inlineStr"/>
       <c r="L259" t="inlineStr"/>
       <c r="M259" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="N259" t="inlineStr"/>
       <c r="O259" t="inlineStr"/>
@@ -25911,7 +25881,7 @@
       </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>11:59 PM</t>
+          <t>11:00 PM</t>
         </is>
       </c>
       <c r="T259" t="inlineStr">
@@ -25931,10 +25901,10 @@
         </is>
       </c>
       <c r="X259" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="Y259" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z259" t="n">
         <v>0.65</v>
@@ -25946,7 +25916,7 @@
         <v>2</v>
       </c>
       <c r="AC259" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.748</v>
       </c>
       <c r="AD259" t="n">
         <v>1</v>
@@ -26011,7 +25981,7 @@
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>5:05 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="T260" t="inlineStr">
@@ -26111,7 +26081,7 @@
       </c>
       <c r="S261" t="inlineStr">
         <is>
-          <t>5:05 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="T261" t="inlineStr">
@@ -26211,7 +26181,7 @@
       </c>
       <c r="S262" t="inlineStr">
         <is>
-          <t>5:05 PM</t>
+          <t>5:15 PM</t>
         </is>
       </c>
       <c r="T262" t="inlineStr">
@@ -26298,7 +26268,7 @@
       <c r="K263" t="inlineStr"/>
       <c r="L263" t="inlineStr"/>
       <c r="M263" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N263" t="inlineStr"/>
       <c r="O263" t="inlineStr"/>
@@ -26331,7 +26301,7 @@
         </is>
       </c>
       <c r="X263" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="Y263" t="n">
         <v>0</v>
@@ -26346,7 +26316,7 @@
         <v>2</v>
       </c>
       <c r="AC263" t="n">
-        <v>0.3365</v>
+        <v>0.3095</v>
       </c>
       <c r="AD263" t="n">
         <v>1</v>
@@ -26398,7 +26368,7 @@
       <c r="K264" t="inlineStr"/>
       <c r="L264" t="inlineStr"/>
       <c r="M264" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N264" t="inlineStr"/>
       <c r="O264" t="inlineStr"/>
@@ -26431,10 +26401,10 @@
         </is>
       </c>
       <c r="X264" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="Y264" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z264" t="n">
         <v>0.38</v>
@@ -26446,7 +26416,7 @@
         <v>3</v>
       </c>
       <c r="AC264" t="n">
-        <v>0.291</v>
+        <v>0.2395</v>
       </c>
       <c r="AD264" t="n">
         <v>1</v>
@@ -26498,7 +26468,7 @@
       <c r="K265" t="inlineStr"/>
       <c r="L265" t="inlineStr"/>
       <c r="M265" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N265" t="inlineStr"/>
       <c r="O265" t="inlineStr"/>
@@ -26531,7 +26501,7 @@
         </is>
       </c>
       <c r="X265" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="Y265" t="n">
         <v>0</v>
@@ -26546,7 +26516,7 @@
         <v>1</v>
       </c>
       <c r="AC265" t="n">
-        <v>0.377</v>
+        <v>0.35</v>
       </c>
       <c r="AD265" t="n">
         <v>1</v>
@@ -26598,7 +26568,7 @@
       <c r="K266" t="inlineStr"/>
       <c r="L266" t="inlineStr"/>
       <c r="M266" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="N266" t="inlineStr"/>
       <c r="O266" t="inlineStr"/>
@@ -26631,10 +26601,10 @@
         </is>
       </c>
       <c r="X266" t="n">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="Y266" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="Z266" t="n">
         <v>0.79</v>
@@ -26643,10 +26613,10 @@
         <v>0.68</v>
       </c>
       <c r="AB266" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC266" t="n">
-        <v>0.833</v>
+        <v>0.5785</v>
       </c>
       <c r="AD266" t="n">
         <v>1</v>
@@ -26698,7 +26668,7 @@
       <c r="K267" t="inlineStr"/>
       <c r="L267" t="inlineStr"/>
       <c r="M267" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="N267" t="inlineStr"/>
       <c r="O267" t="inlineStr"/>
@@ -26731,10 +26701,10 @@
         </is>
       </c>
       <c r="X267" t="n">
-        <v>0.82</v>
+        <v>0.36</v>
       </c>
       <c r="Y267" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="Z267" t="n">
         <v>1</v>
@@ -26743,10 +26713,10 @@
         <v>1</v>
       </c>
       <c r="AB267" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC267" t="n">
-        <v>0.89</v>
+        <v>0.5665</v>
       </c>
       <c r="AD267" t="n">
         <v>1</v>
@@ -26798,7 +26768,7 @@
       <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr"/>
       <c r="M268" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="N268" t="inlineStr"/>
       <c r="O268" t="inlineStr"/>
@@ -26831,10 +26801,10 @@
         </is>
       </c>
       <c r="X268" t="n">
-        <v>0.93</v>
+        <v>0.7</v>
       </c>
       <c r="Y268" t="n">
-        <v>0.84</v>
+        <v>0.31</v>
       </c>
       <c r="Z268" t="n">
         <v>0.74</v>
@@ -26846,7 +26816,7 @@
         <v>3</v>
       </c>
       <c r="AC268" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.5595</v>
       </c>
       <c r="AD268" t="n">
         <v>1</v>
@@ -27198,7 +27168,7 @@
       <c r="K272" t="inlineStr"/>
       <c r="L272" t="inlineStr"/>
       <c r="M272" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="N272" t="inlineStr"/>
       <c r="O272" t="inlineStr"/>
@@ -27231,10 +27201,10 @@
         </is>
       </c>
       <c r="X272" t="n">
-        <v>0.95</v>
+        <v>0.67</v>
       </c>
       <c r="Y272" t="n">
-        <v>0.91</v>
+        <v>0.36</v>
       </c>
       <c r="Z272" t="n">
         <v>0.54</v>
@@ -27243,10 +27213,10 @@
         <v>0.34</v>
       </c>
       <c r="AB272" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC272" t="n">
-        <v>0.7625</v>
+        <v>0.486</v>
       </c>
       <c r="AD272" t="n">
         <v>1</v>
@@ -27298,7 +27268,7 @@
       <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr"/>
       <c r="M273" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="N273" t="inlineStr"/>
       <c r="O273" t="inlineStr"/>
@@ -27331,10 +27301,10 @@
         </is>
       </c>
       <c r="X273" t="n">
-        <v>0.86</v>
+        <v>0.3</v>
       </c>
       <c r="Y273" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="Z273" t="n">
         <v>0.74</v>
@@ -27343,10 +27313,10 @@
         <v>0.62</v>
       </c>
       <c r="AB273" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC273" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.4395</v>
       </c>
       <c r="AD273" t="n">
         <v>1</v>
@@ -27398,7 +27368,7 @@
       <c r="K274" t="inlineStr"/>
       <c r="L274" t="inlineStr"/>
       <c r="M274" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="N274" t="inlineStr"/>
       <c r="O274" t="inlineStr"/>
@@ -27431,10 +27401,10 @@
         </is>
       </c>
       <c r="X274" t="n">
-        <v>0.86</v>
+        <v>0.3</v>
       </c>
       <c r="Y274" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="Z274" t="n">
         <v>1</v>
@@ -27446,7 +27416,7 @@
         <v>1</v>
       </c>
       <c r="AC274" t="n">
-        <v>0.9229999999999999</v>
+        <v>0.5485</v>
       </c>
       <c r="AD274" t="n">
         <v>1</v>
@@ -27498,7 +27468,7 @@
       <c r="K275" t="inlineStr"/>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N275" t="inlineStr"/>
       <c r="O275" t="inlineStr"/>
@@ -27531,7 +27501,7 @@
         </is>
       </c>
       <c r="X275" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="Y275" t="n">
         <v>0</v>
@@ -27546,7 +27516,7 @@
         <v>2</v>
       </c>
       <c r="AC275" t="n">
-        <v>0.313</v>
+        <v>0.268</v>
       </c>
       <c r="AD275" t="n">
         <v>1</v>
@@ -27598,7 +27568,7 @@
       <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N276" t="inlineStr"/>
       <c r="O276" t="inlineStr"/>
@@ -27631,10 +27601,10 @@
         </is>
       </c>
       <c r="X276" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="Y276" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z276" t="n">
         <v>0.25</v>
@@ -27646,7 +27616,7 @@
         <v>3</v>
       </c>
       <c r="AC276" t="n">
-        <v>0.256</v>
+        <v>0.1865</v>
       </c>
       <c r="AD276" t="n">
         <v>1</v>
@@ -27698,7 +27668,7 @@
       <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr"/>
       <c r="M277" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N277" t="inlineStr"/>
       <c r="O277" t="inlineStr"/>
@@ -28698,7 +28668,7 @@
       <c r="K287" t="inlineStr"/>
       <c r="L287" t="inlineStr"/>
       <c r="M287" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N287" t="inlineStr"/>
       <c r="O287" t="inlineStr"/>
@@ -28731,10 +28701,10 @@
         </is>
       </c>
       <c r="X287" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="Y287" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Z287" t="n">
         <v>0.51</v>
@@ -28746,7 +28716,7 @@
         <v>3</v>
       </c>
       <c r="AC287" t="n">
-        <v>0.3345</v>
+        <v>0.252</v>
       </c>
       <c r="AD287" t="n">
         <v>1</v>
@@ -28798,7 +28768,7 @@
       <c r="K288" t="inlineStr"/>
       <c r="L288" t="inlineStr"/>
       <c r="M288" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N288" t="inlineStr"/>
       <c r="O288" t="inlineStr"/>
@@ -28831,10 +28801,10 @@
         </is>
       </c>
       <c r="X288" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="Y288" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Z288" t="n">
         <v>0.79</v>
@@ -28846,7 +28816,7 @@
         <v>2</v>
       </c>
       <c r="AC288" t="n">
-        <v>0.4415</v>
+        <v>0.359</v>
       </c>
       <c r="AD288" t="n">
         <v>1</v>
@@ -28898,7 +28868,7 @@
       <c r="K289" t="inlineStr"/>
       <c r="L289" t="inlineStr"/>
       <c r="M289" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N289" t="inlineStr"/>
       <c r="O289" t="inlineStr"/>
@@ -28931,10 +28901,10 @@
         </is>
       </c>
       <c r="X289" t="n">
-        <v>0.43</v>
+        <v>0.33</v>
       </c>
       <c r="Y289" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="Z289" t="n">
         <v>1</v>
@@ -28946,7 +28916,7 @@
         <v>1</v>
       </c>
       <c r="AC289" t="n">
-        <v>0.5315</v>
+        <v>0.4490000000000001</v>
       </c>
       <c r="AD289" t="n">
         <v>1</v>
@@ -29611,7 +29581,7 @@
       </c>
       <c r="S296" t="inlineStr">
         <is>
-          <t>12:05 AM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="T296" t="inlineStr">
@@ -29711,7 +29681,7 @@
       </c>
       <c r="S297" t="inlineStr">
         <is>
-          <t>12:05 AM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="T297" t="inlineStr">
@@ -29811,7 +29781,7 @@
       </c>
       <c r="S298" t="inlineStr">
         <is>
-          <t>12:05 AM</t>
+          <t>12:00 AM</t>
         </is>
       </c>
       <c r="T298" t="inlineStr">
@@ -30798,7 +30768,7 @@
       <c r="K308" t="inlineStr"/>
       <c r="L308" t="inlineStr"/>
       <c r="M308" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="N308" t="inlineStr"/>
       <c r="O308" t="inlineStr"/>
@@ -30811,7 +30781,7 @@
       </c>
       <c r="S308" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="T308" t="inlineStr">
@@ -30831,10 +30801,10 @@
         </is>
       </c>
       <c r="X308" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="Y308" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="Z308" t="n">
         <v>0.85</v>
@@ -30843,10 +30813,10 @@
         <v>0.67</v>
       </c>
       <c r="AB308" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC308" t="n">
-        <v>0.7170000000000001</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="AD308" t="n">
         <v>1</v>
@@ -30898,7 +30868,7 @@
       <c r="K309" t="inlineStr"/>
       <c r="L309" t="inlineStr"/>
       <c r="M309" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="N309" t="inlineStr"/>
       <c r="O309" t="inlineStr"/>
@@ -30911,7 +30881,7 @@
       </c>
       <c r="S309" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="T309" t="inlineStr">
@@ -30931,10 +30901,10 @@
         </is>
       </c>
       <c r="X309" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="Y309" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z309" t="n">
         <v>0.71</v>
@@ -30946,7 +30916,7 @@
         <v>3</v>
       </c>
       <c r="AC309" t="n">
-        <v>0.653</v>
+        <v>0.623</v>
       </c>
       <c r="AD309" t="n">
         <v>1</v>
@@ -30998,7 +30968,7 @@
       <c r="K310" t="inlineStr"/>
       <c r="L310" t="inlineStr"/>
       <c r="M310" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="N310" t="inlineStr"/>
       <c r="O310" t="inlineStr"/>
@@ -31011,7 +30981,7 @@
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>7pm</t>
+          <t>7:00 PM</t>
         </is>
       </c>
       <c r="T310" t="inlineStr">
@@ -31031,10 +31001,10 @@
         </is>
       </c>
       <c r="X310" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="Y310" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="Z310" t="n">
         <v>1</v>
@@ -31043,10 +31013,10 @@
         <v>1</v>
       </c>
       <c r="AB310" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC310" t="n">
-        <v>0.7245</v>
+        <v>0.6855000000000001</v>
       </c>
       <c r="AD310" t="n">
         <v>1</v>
@@ -31398,7 +31368,7 @@
       <c r="K314" t="inlineStr"/>
       <c r="L314" t="inlineStr"/>
       <c r="M314" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N314" t="inlineStr"/>
       <c r="O314" t="inlineStr"/>
@@ -31431,10 +31401,10 @@
         </is>
       </c>
       <c r="X314" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Y314" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="Z314" t="n">
         <v>0.63</v>
@@ -31446,7 +31416,7 @@
         <v>2</v>
       </c>
       <c r="AC314" t="n">
-        <v>0.4475</v>
+        <v>0.5365</v>
       </c>
       <c r="AD314" t="n">
         <v>1</v>
@@ -31498,7 +31468,7 @@
       <c r="K315" t="inlineStr"/>
       <c r="L315" t="inlineStr"/>
       <c r="M315" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N315" t="inlineStr"/>
       <c r="O315" t="inlineStr"/>
@@ -31531,10 +31501,10 @@
         </is>
       </c>
       <c r="X315" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Y315" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="Z315" t="n">
         <v>0.7</v>
@@ -31546,7 +31516,7 @@
         <v>1</v>
       </c>
       <c r="AC315" t="n">
-        <v>0.4775</v>
+        <v>0.5595</v>
       </c>
       <c r="AD315" t="n">
         <v>1</v>
@@ -31598,7 +31568,7 @@
       <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr"/>
       <c r="M316" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="N316" t="inlineStr"/>
       <c r="O316" t="inlineStr"/>
@@ -31631,10 +31601,10 @@
         </is>
       </c>
       <c r="X316" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
       <c r="Y316" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="Z316" t="n">
         <v>0.51</v>
@@ -31646,7 +31616,7 @@
         <v>3</v>
       </c>
       <c r="AC316" t="n">
-        <v>0.422</v>
+        <v>0.511</v>
       </c>
       <c r="AD316" t="n">
         <v>1</v>
@@ -31698,7 +31668,7 @@
       <c r="K317" t="inlineStr"/>
       <c r="L317" t="inlineStr"/>
       <c r="M317" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="N317" t="inlineStr"/>
       <c r="O317" t="inlineStr"/>
@@ -31731,10 +31701,10 @@
         </is>
       </c>
       <c r="X317" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="Y317" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="Z317" t="n">
         <v>0.91</v>
@@ -31746,7 +31716,7 @@
         <v>2</v>
       </c>
       <c r="AC317" t="n">
-        <v>0.702</v>
+        <v>0.9195</v>
       </c>
       <c r="AD317" t="n">
         <v>1</v>
@@ -31798,7 +31768,7 @@
       <c r="K318" t="inlineStr"/>
       <c r="L318" t="inlineStr"/>
       <c r="M318" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="N318" t="inlineStr"/>
       <c r="O318" t="inlineStr"/>
@@ -31831,10 +31801,10 @@
         </is>
       </c>
       <c r="X318" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="Y318" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="Z318" t="n">
         <v>0.78</v>
@@ -31846,7 +31816,7 @@
         <v>3</v>
       </c>
       <c r="AC318" t="n">
-        <v>0.649</v>
+        <v>0.8665</v>
       </c>
       <c r="AD318" t="n">
         <v>1</v>
@@ -31898,7 +31868,7 @@
       <c r="K319" t="inlineStr"/>
       <c r="L319" t="inlineStr"/>
       <c r="M319" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="N319" t="inlineStr"/>
       <c r="O319" t="inlineStr"/>
@@ -31931,10 +31901,10 @@
         </is>
       </c>
       <c r="X319" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="Y319" t="n">
-        <v>0.47</v>
+        <v>0.92</v>
       </c>
       <c r="Z319" t="n">
         <v>0.96</v>
@@ -31946,7 +31916,7 @@
         <v>1</v>
       </c>
       <c r="AC319" t="n">
-        <v>0.724</v>
+        <v>0.9415</v>
       </c>
       <c r="AD319" t="n">
         <v>1</v>
@@ -31998,7 +31968,7 @@
       <c r="K320" t="inlineStr"/>
       <c r="L320" t="inlineStr"/>
       <c r="M320" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N320" t="inlineStr"/>
       <c r="O320" t="inlineStr"/>
@@ -32031,7 +32001,7 @@
         </is>
       </c>
       <c r="X320" t="n">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="Y320" t="n">
         <v>0</v>
@@ -32043,10 +32013,10 @@
         <v>0.25</v>
       </c>
       <c r="AB320" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC320" t="n">
-        <v>0.2755</v>
+        <v>0.2905</v>
       </c>
       <c r="AD320" t="n">
         <v>1</v>
@@ -32098,7 +32068,7 @@
       <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr"/>
       <c r="M321" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N321" t="inlineStr"/>
       <c r="O321" t="inlineStr"/>
@@ -32143,7 +32113,7 @@
         <v>0.75</v>
       </c>
       <c r="AB321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC321" t="n">
         <v>0.2785</v>
@@ -32198,7 +32168,7 @@
       <c r="K322" t="inlineStr"/>
       <c r="L322" t="inlineStr"/>
       <c r="M322" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="N322" t="inlineStr"/>
       <c r="O322" t="inlineStr"/>
@@ -32598,7 +32568,7 @@
       <c r="K326" t="inlineStr"/>
       <c r="L326" t="inlineStr"/>
       <c r="M326" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="N326" t="inlineStr"/>
       <c r="O326" t="inlineStr"/>
@@ -32611,7 +32581,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9am</t>
         </is>
       </c>
       <c r="T326" t="inlineStr">
@@ -32631,10 +32601,10 @@
         </is>
       </c>
       <c r="X326" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="Y326" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="Z326" t="n">
         <v>0.82</v>
@@ -32646,7 +32616,7 @@
         <v>2</v>
       </c>
       <c r="AC326" t="n">
-        <v>0.61</v>
+        <v>0.7110000000000001</v>
       </c>
       <c r="AD326" t="n">
         <v>1</v>
@@ -32698,7 +32668,7 @@
       <c r="K327" t="inlineStr"/>
       <c r="L327" t="inlineStr"/>
       <c r="M327" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="N327" t="inlineStr"/>
       <c r="O327" t="inlineStr"/>
@@ -32711,7 +32681,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9am</t>
         </is>
       </c>
       <c r="T327" t="inlineStr">
@@ -32731,10 +32701,10 @@
         </is>
       </c>
       <c r="X327" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Y327" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="Z327" t="n">
         <v>0.58</v>
@@ -32746,7 +32716,7 @@
         <v>3</v>
       </c>
       <c r="AC327" t="n">
-        <v>0.289</v>
+        <v>0.426</v>
       </c>
       <c r="AD327" t="n">
         <v>1</v>
@@ -32798,7 +32768,7 @@
       <c r="K328" t="inlineStr"/>
       <c r="L328" t="inlineStr"/>
       <c r="M328" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="N328" t="inlineStr"/>
       <c r="O328" t="inlineStr"/>
@@ -32811,7 +32781,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>9:00 AM</t>
+          <t>9am</t>
         </is>
       </c>
       <c r="T328" t="inlineStr">
@@ -32831,10 +32801,10 @@
         </is>
       </c>
       <c r="X328" t="n">
-        <v>0.76</v>
+        <v>0.84</v>
       </c>
       <c r="Y328" t="n">
-        <v>0.31</v>
+        <v>0.53</v>
       </c>
       <c r="Z328" t="n">
         <v>0.9399999999999999</v>
@@ -32846,7 +32816,7 @@
         <v>1</v>
       </c>
       <c r="AC328" t="n">
-        <v>0.661</v>
+        <v>0.762</v>
       </c>
       <c r="AD328" t="n">
         <v>1</v>
@@ -33498,7 +33468,7 @@
       <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr"/>
       <c r="M335" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N335" t="inlineStr"/>
       <c r="O335" t="inlineStr"/>
@@ -33531,10 +33501,10 @@
         </is>
       </c>
       <c r="X335" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="Y335" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z335" t="n">
         <v>0.43</v>
@@ -33546,7 +33516,7 @@
         <v>3</v>
       </c>
       <c r="AC335" t="n">
-        <v>0.3415</v>
+        <v>0.3080000000000001</v>
       </c>
       <c r="AD335" t="n">
         <v>1</v>
@@ -33598,7 +33568,7 @@
       <c r="K336" t="inlineStr"/>
       <c r="L336" t="inlineStr"/>
       <c r="M336" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N336" t="inlineStr"/>
       <c r="O336" t="inlineStr"/>
@@ -33631,7 +33601,7 @@
         </is>
       </c>
       <c r="X336" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="Y336" t="n">
         <v>0</v>
@@ -33646,7 +33616,7 @@
         <v>2</v>
       </c>
       <c r="AC336" t="n">
-        <v>0.357</v>
+        <v>0.348</v>
       </c>
       <c r="AD336" t="n">
         <v>1</v>
@@ -33698,7 +33668,7 @@
       <c r="K337" t="inlineStr"/>
       <c r="L337" t="inlineStr"/>
       <c r="M337" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N337" t="inlineStr"/>
       <c r="O337" t="inlineStr"/>
@@ -33731,7 +33701,7 @@
         </is>
       </c>
       <c r="X337" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="Y337" t="n">
         <v>0</v>
@@ -33746,7 +33716,7 @@
         <v>1</v>
       </c>
       <c r="AC337" t="n">
-        <v>0.554</v>
+        <v>0.545</v>
       </c>
       <c r="AD337" t="n">
         <v>1</v>
@@ -33798,7 +33768,7 @@
       <c r="K338" t="inlineStr"/>
       <c r="L338" t="inlineStr"/>
       <c r="M338" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N338" t="inlineStr"/>
       <c r="O338" t="inlineStr"/>
@@ -33831,10 +33801,10 @@
         </is>
       </c>
       <c r="X338" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="Y338" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="Z338" t="n">
         <v>1</v>
@@ -33846,7 +33816,7 @@
         <v>1</v>
       </c>
       <c r="AC338" t="n">
-        <v>0.7560000000000001</v>
+        <v>0.7395</v>
       </c>
       <c r="AD338" t="n">
         <v>1</v>
@@ -33898,7 +33868,7 @@
       <c r="K339" t="inlineStr"/>
       <c r="L339" t="inlineStr"/>
       <c r="M339" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N339" t="inlineStr"/>
       <c r="O339" t="inlineStr"/>
@@ -33931,10 +33901,10 @@
         </is>
       </c>
       <c r="X339" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="Y339" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z339" t="n">
         <v>0.55</v>
@@ -33946,7 +33916,7 @@
         <v>3</v>
       </c>
       <c r="AC339" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5505</v>
       </c>
       <c r="AD339" t="n">
         <v>1</v>
@@ -33998,7 +33968,7 @@
       <c r="K340" t="inlineStr"/>
       <c r="L340" t="inlineStr"/>
       <c r="M340" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N340" t="inlineStr"/>
       <c r="O340" t="inlineStr"/>
@@ -34031,10 +34001,10 @@
         </is>
       </c>
       <c r="X340" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="Y340" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="Z340" t="n">
         <v>0.78</v>
@@ -34046,7 +34016,7 @@
         <v>2</v>
       </c>
       <c r="AC340" t="n">
-        <v>0.6625000000000001</v>
+        <v>0.6460000000000001</v>
       </c>
       <c r="AD340" t="n">
         <v>1</v>
@@ -34098,7 +34068,7 @@
       <c r="K341" t="inlineStr"/>
       <c r="L341" t="inlineStr"/>
       <c r="M341" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N341" t="inlineStr"/>
       <c r="O341" t="inlineStr"/>
@@ -34131,10 +34101,10 @@
         </is>
       </c>
       <c r="X341" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Y341" t="n">
-        <v>0.74</v>
+        <v>0.5</v>
       </c>
       <c r="Z341" t="n">
         <v>0.38</v>
@@ -34146,7 +34116,7 @@
         <v>3</v>
       </c>
       <c r="AC341" t="n">
-        <v>0.5974999999999999</v>
+        <v>0.4655</v>
       </c>
       <c r="AD341" t="n">
         <v>1</v>
@@ -34198,7 +34168,7 @@
       <c r="K342" t="inlineStr"/>
       <c r="L342" t="inlineStr"/>
       <c r="M342" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N342" t="inlineStr"/>
       <c r="O342" t="inlineStr"/>
@@ -34231,10 +34201,10 @@
         </is>
       </c>
       <c r="X342" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Y342" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="Z342" t="n">
         <v>1</v>
@@ -34246,7 +34216,7 @@
         <v>1</v>
       </c>
       <c r="AC342" t="n">
-        <v>0.8384999999999999</v>
+        <v>0.7065</v>
       </c>
       <c r="AD342" t="n">
         <v>1</v>
@@ -34298,7 +34268,7 @@
       <c r="K343" t="inlineStr"/>
       <c r="L343" t="inlineStr"/>
       <c r="M343" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="N343" t="inlineStr"/>
       <c r="O343" t="inlineStr"/>
@@ -34331,10 +34301,10 @@
         </is>
       </c>
       <c r="X343" t="n">
-        <v>0.8</v>
+        <v>0.64</v>
       </c>
       <c r="Y343" t="n">
-        <v>0.71</v>
+        <v>0.47</v>
       </c>
       <c r="Z343" t="n">
         <v>0.79</v>
@@ -34346,7 +34316,7 @@
         <v>2</v>
       </c>
       <c r="AC343" t="n">
-        <v>0.7484999999999999</v>
+        <v>0.6164999999999999</v>
       </c>
       <c r="AD343" t="n">
         <v>1</v>
@@ -34398,7 +34368,7 @@
       <c r="K344" t="inlineStr"/>
       <c r="L344" t="inlineStr"/>
       <c r="M344" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="N344" t="inlineStr"/>
       <c r="O344" t="inlineStr"/>
@@ -34411,7 +34381,7 @@
       </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7pm</t>
         </is>
       </c>
       <c r="T344" t="inlineStr">
@@ -34431,10 +34401,10 @@
         </is>
       </c>
       <c r="X344" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="Y344" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Z344" t="n">
         <v>0.85</v>
@@ -34446,7 +34416,7 @@
         <v>2</v>
       </c>
       <c r="AC344" t="n">
-        <v>0.627</v>
+        <v>0.66</v>
       </c>
       <c r="AD344" t="n">
         <v>1</v>
@@ -34498,7 +34468,7 @@
       <c r="K345" t="inlineStr"/>
       <c r="L345" t="inlineStr"/>
       <c r="M345" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="N345" t="inlineStr"/>
       <c r="O345" t="inlineStr"/>
@@ -34511,7 +34481,7 @@
       </c>
       <c r="S345" t="inlineStr">
         <is>
-          <t>7:00 PM</t>
+          <t>7pm</t>
         </is>
       </c>
       <c r="T345" t="inlineStr">
@@ -34531,10 +34501,10 @@
         </is>
       </c>
       <c r="X345" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="Y345" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z345" t="n">
         <v>0.76</v>
@@ -34546,7 +34516,7 @@
         <v>3</v>
       </c>
       <c r="AC345" t="n">
-        <v>0.5835</v>
+        <v>0.6165</v>
       </c>
       <c r="AD345" t="n">
         <v>1</v>
@@ -34598,7 +34568,7 @@
       <c r="K346" t="inlineStr"/>
       <c r="L346" t="inlineStr"/>
       <c r="M346" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="N346" t="inlineStr"/>
       <c r="O346" t="inlineStr"/>
@@ -34611,30 +34581,30 @@
       </c>
       <c r="S346" t="inlineStr">
         <is>
+          <t>7pm</t>
+        </is>
+      </c>
+      <c r="T346" t="inlineStr">
+        <is>
+          <t>ApplianceGroundTruthCalculator</t>
+        </is>
+      </c>
+      <c r="U346" t="b">
+        <v>0</v>
+      </c>
+      <c r="V346" t="b">
+        <v>0</v>
+      </c>
+      <c r="W346" t="inlineStr">
+        <is>
           <t>7:00 PM</t>
         </is>
       </c>
-      <c r="T346" t="inlineStr">
-        <is>
-          <t>ApplianceGroundTruthCalculator</t>
-        </is>
-      </c>
-      <c r="U346" t="b">
-        <v>0</v>
-      </c>
-      <c r="V346" t="b">
-        <v>0</v>
-      </c>
-      <c r="W346" t="inlineStr">
-        <is>
-          <t>7:00 PM</t>
-        </is>
-      </c>
       <c r="X346" t="n">
-        <v>0.64</v>
+        <v>0.68</v>
       </c>
       <c r="Y346" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="Z346" t="n">
         <v>1</v>
@@ -34646,7 +34616,7 @@
         <v>1</v>
       </c>
       <c r="AC346" t="n">
-        <v>0.7065</v>
+        <v>0.7395</v>
       </c>
       <c r="AD346" t="n">
         <v>1</v>
@@ -34698,7 +34668,7 @@
       <c r="K347" t="inlineStr"/>
       <c r="L347" t="inlineStr"/>
       <c r="M347" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="N347" t="inlineStr"/>
       <c r="O347" t="inlineStr"/>
@@ -34731,10 +34701,10 @@
         </is>
       </c>
       <c r="X347" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="Y347" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Z347" t="n">
         <v>0.43</v>
@@ -34746,7 +34716,7 @@
         <v>3</v>
       </c>
       <c r="AC347" t="n">
-        <v>0.537</v>
+        <v>0.504</v>
       </c>
       <c r="AD347" t="n">
         <v>1</v>
@@ -34798,7 +34768,7 @@
       <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr"/>
       <c r="M348" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="N348" t="inlineStr"/>
       <c r="O348" t="inlineStr"/>
@@ -34831,10 +34801,10 @@
         </is>
       </c>
       <c r="X348" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="Y348" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Z348" t="n">
         <v>1</v>
@@ -34846,7 +34816,7 @@
         <v>1</v>
       </c>
       <c r="AC348" t="n">
-        <v>0.7395</v>
+        <v>0.7065</v>
       </c>
       <c r="AD348" t="n">
         <v>1</v>
@@ -34898,7 +34868,7 @@
       <c r="K349" t="inlineStr"/>
       <c r="L349" t="inlineStr"/>
       <c r="M349" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="N349" t="inlineStr"/>
       <c r="O349" t="inlineStr"/>
@@ -34931,10 +34901,10 @@
         </is>
       </c>
       <c r="X349" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="Y349" t="n">
-        <v>0.53</v>
+        <v>0.47</v>
       </c>
       <c r="Z349" t="n">
         <v>0.7</v>
@@ -34946,7 +34916,7 @@
         <v>2</v>
       </c>
       <c r="AC349" t="n">
-        <v>0.615</v>
+        <v>0.582</v>
       </c>
       <c r="AD349" t="n">
         <v>1</v>
@@ -34998,7 +34968,7 @@
       <c r="K350" t="inlineStr"/>
       <c r="L350" t="inlineStr"/>
       <c r="M350" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N350" t="inlineStr"/>
       <c r="O350" t="inlineStr"/>
@@ -35031,10 +35001,10 @@
         </is>
       </c>
       <c r="X350" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="Y350" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z350" t="n">
         <v>0.43</v>
@@ -35043,10 +35013,10 @@
         <v>0.31</v>
       </c>
       <c r="AB350" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC350" t="n">
-        <v>0.2945</v>
+        <v>0.352</v>
       </c>
       <c r="AD350" t="n">
         <v>1</v>
@@ -35098,7 +35068,7 @@
       <c r="K351" t="inlineStr"/>
       <c r="L351" t="inlineStr"/>
       <c r="M351" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N351" t="inlineStr"/>
       <c r="O351" t="inlineStr"/>
@@ -35143,7 +35113,7 @@
         <v>1</v>
       </c>
       <c r="AB351" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC351" t="n">
         <v>0.35</v>
@@ -35198,7 +35168,7 @@
       <c r="K352" t="inlineStr"/>
       <c r="L352" t="inlineStr"/>
       <c r="M352" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N352" t="inlineStr"/>
       <c r="O352" t="inlineStr"/>
@@ -35231,7 +35201,7 @@
         </is>
       </c>
       <c r="X352" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="Y352" t="n">
         <v>0</v>
@@ -35246,7 +35216,7 @@
         <v>1</v>
       </c>
       <c r="AC352" t="n">
-        <v>0.3615</v>
+        <v>0.3945</v>
       </c>
       <c r="AD352" t="n">
         <v>1</v>
@@ -35298,7 +35268,7 @@
       <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr"/>
       <c r="M353" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N353" t="inlineStr"/>
       <c r="O353" t="inlineStr"/>
@@ -35331,10 +35301,10 @@
         </is>
       </c>
       <c r="X353" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y353" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="Z353" t="n">
         <v>0.78</v>
@@ -35346,7 +35316,7 @@
         <v>1</v>
       </c>
       <c r="AC353" t="n">
-        <v>0.8780000000000001</v>
+        <v>0.8645</v>
       </c>
       <c r="AD353" t="n">
         <v>1</v>
@@ -35398,7 +35368,7 @@
       <c r="K354" t="inlineStr"/>
       <c r="L354" t="inlineStr"/>
       <c r="M354" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N354" t="inlineStr"/>
       <c r="O354" t="inlineStr"/>
@@ -35431,10 +35401,10 @@
         </is>
       </c>
       <c r="X354" t="n">
-        <v>0.85</v>
+        <v>0.83</v>
       </c>
       <c r="Y354" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z354" t="n">
         <v>0.55</v>
@@ -35446,7 +35416,7 @@
         <v>3</v>
       </c>
       <c r="AC354" t="n">
-        <v>0.7174999999999999</v>
+        <v>0.701</v>
       </c>
       <c r="AD354" t="n">
         <v>1</v>
@@ -35498,7 +35468,7 @@
       <c r="K355" t="inlineStr"/>
       <c r="L355" t="inlineStr"/>
       <c r="M355" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N355" t="inlineStr"/>
       <c r="O355" t="inlineStr"/>
@@ -35531,10 +35501,10 @@
         </is>
       </c>
       <c r="X355" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Y355" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z355" t="n">
         <v>0.55</v>
@@ -35546,7 +35516,7 @@
         <v>2</v>
       </c>
       <c r="AC355" t="n">
-        <v>0.7474999999999999</v>
+        <v>0.7339999999999999</v>
       </c>
       <c r="AD355" t="n">
         <v>1</v>
@@ -35598,7 +35568,7 @@
       <c r="K356" t="inlineStr"/>
       <c r="L356" t="inlineStr"/>
       <c r="M356" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N356" t="inlineStr"/>
       <c r="O356" t="inlineStr"/>
@@ -35631,10 +35601,10 @@
         </is>
       </c>
       <c r="X356" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="Y356" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z356" t="n">
         <v>0.59</v>
@@ -35646,7 +35616,7 @@
         <v>2</v>
       </c>
       <c r="AC356" t="n">
-        <v>0.754</v>
+        <v>0.7404999999999999</v>
       </c>
       <c r="AD356" t="n">
         <v>1</v>
@@ -35698,7 +35668,7 @@
       <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr"/>
       <c r="M357" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N357" t="inlineStr"/>
       <c r="O357" t="inlineStr"/>
@@ -35731,10 +35701,10 @@
         </is>
       </c>
       <c r="X357" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="Y357" t="n">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="Z357" t="n">
         <v>0.78</v>
@@ -35746,7 +35716,7 @@
         <v>1</v>
       </c>
       <c r="AC357" t="n">
-        <v>0.857</v>
+        <v>0.8435000000000001</v>
       </c>
       <c r="AD357" t="n">
         <v>1</v>
@@ -35798,7 +35768,7 @@
       <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr"/>
       <c r="M358" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N358" t="inlineStr"/>
       <c r="O358" t="inlineStr"/>
@@ -35831,10 +35801,10 @@
         </is>
       </c>
       <c r="X358" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="Y358" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Z358" t="n">
         <v>0.63</v>
@@ -35846,7 +35816,7 @@
         <v>3</v>
       </c>
       <c r="AC358" t="n">
-        <v>0.732</v>
+        <v>0.7124999999999999</v>
       </c>
       <c r="AD358" t="n">
         <v>1</v>
@@ -35898,7 +35868,7 @@
       <c r="K359" t="inlineStr"/>
       <c r="L359" t="inlineStr"/>
       <c r="M359" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N359" t="inlineStr"/>
       <c r="O359" t="inlineStr"/>
@@ -35931,10 +35901,10 @@
         </is>
       </c>
       <c r="X359" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y359" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Z359" t="n">
         <v>0.78</v>
@@ -35946,7 +35916,7 @@
         <v>1</v>
       </c>
       <c r="AC359" t="n">
-        <v>0.4305</v>
+        <v>0.476</v>
       </c>
       <c r="AD359" t="n">
         <v>1</v>
@@ -35998,7 +35968,7 @@
       <c r="K360" t="inlineStr"/>
       <c r="L360" t="inlineStr"/>
       <c r="M360" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N360" t="inlineStr"/>
       <c r="O360" t="inlineStr"/>
@@ -36031,7 +36001,7 @@
         </is>
       </c>
       <c r="X360" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Y360" t="n">
         <v>0</v>
@@ -36046,7 +36016,7 @@
         <v>3</v>
       </c>
       <c r="AC360" t="n">
-        <v>0.1685</v>
+        <v>0.1955</v>
       </c>
       <c r="AD360" t="n">
         <v>1</v>
@@ -36098,7 +36068,7 @@
       <c r="K361" t="inlineStr"/>
       <c r="L361" t="inlineStr"/>
       <c r="M361" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N361" t="inlineStr"/>
       <c r="O361" t="inlineStr"/>
@@ -36131,7 +36101,7 @@
         </is>
       </c>
       <c r="X361" t="n">
-        <v>0.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Y361" t="n">
         <v>0</v>
@@ -36146,7 +36116,7 @@
         <v>2</v>
       </c>
       <c r="AC361" t="n">
-        <v>0.359</v>
+        <v>0.3800000000000001</v>
       </c>
       <c r="AD361" t="n">
         <v>1</v>
@@ -36198,7 +36168,7 @@
       <c r="K362" t="inlineStr"/>
       <c r="L362" t="inlineStr"/>
       <c r="M362" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N362" t="inlineStr"/>
       <c r="O362" t="inlineStr"/>
@@ -36211,7 +36181,7 @@
       </c>
       <c r="S362" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>8am</t>
         </is>
       </c>
       <c r="T362" t="inlineStr">
@@ -36231,10 +36201,10 @@
         </is>
       </c>
       <c r="X362" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Y362" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z362" t="n">
         <v>0.78</v>
@@ -36246,7 +36216,7 @@
         <v>2</v>
       </c>
       <c r="AC362" t="n">
-        <v>0.7210000000000001</v>
+        <v>0.7075</v>
       </c>
       <c r="AD362" t="n">
         <v>1</v>
@@ -36298,7 +36268,7 @@
       <c r="K363" t="inlineStr"/>
       <c r="L363" t="inlineStr"/>
       <c r="M363" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N363" t="inlineStr"/>
       <c r="O363" t="inlineStr"/>
@@ -36311,7 +36281,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>8:00 AM</t>
+          <t>8am</t>
         </is>
       </c>
       <c r="T363" t="inlineStr">
@@ -36331,10 +36301,10 @@
         </is>
       </c>
       <c r="X363" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Y363" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z363" t="n">
         <v>0.47</v>
@@ -36346,7 +36316,7 @@
         <v>3</v>
       </c>
       <c r="AC363" t="n">
-        <v>0.602</v>
+        <v>0.5885</v>
       </c>
       <c r="AD363" t="n">
         <v>1</v>
@@ -36398,7 +36368,7 @@
       <c r="K364" t="inlineStr"/>
       <c r="L364" t="inlineStr"/>
       <c r="M364" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N364" t="inlineStr"/>
       <c r="O364" t="inlineStr"/>
@@ -36411,30 +36381,30 @@
       </c>
       <c r="S364" t="inlineStr">
         <is>
+          <t>8am</t>
+        </is>
+      </c>
+      <c r="T364" t="inlineStr">
+        <is>
+          <t>ApplianceGroundTruthCalculator</t>
+        </is>
+      </c>
+      <c r="U364" t="b">
+        <v>0</v>
+      </c>
+      <c r="V364" t="b">
+        <v>0</v>
+      </c>
+      <c r="W364" t="inlineStr">
+        <is>
           <t>8:00 AM</t>
         </is>
       </c>
-      <c r="T364" t="inlineStr">
-        <is>
-          <t>ApplianceGroundTruthCalculator</t>
-        </is>
-      </c>
-      <c r="U364" t="b">
-        <v>0</v>
-      </c>
-      <c r="V364" t="b">
-        <v>0</v>
-      </c>
-      <c r="W364" t="inlineStr">
-        <is>
-          <t>8:00 AM</t>
-        </is>
-      </c>
       <c r="X364" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Y364" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z364" t="n">
         <v>1</v>
@@ -36446,7 +36416,7 @@
         <v>1</v>
       </c>
       <c r="AC364" t="n">
-        <v>0.8145000000000001</v>
+        <v>0.801</v>
       </c>
       <c r="AD364" t="n">
         <v>1</v>
@@ -36498,7 +36468,7 @@
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr"/>
       <c r="M365" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N365" t="inlineStr"/>
       <c r="O365" t="inlineStr"/>
@@ -36531,7 +36501,7 @@
         </is>
       </c>
       <c r="X365" t="n">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
       <c r="Y365" t="n">
         <v>0</v>
@@ -36546,7 +36516,7 @@
         <v>2</v>
       </c>
       <c r="AC365" t="n">
-        <v>0.3685</v>
+        <v>0.3355</v>
       </c>
       <c r="AD365" t="n">
         <v>1</v>
@@ -36598,7 +36568,7 @@
       <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr"/>
       <c r="M366" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N366" t="inlineStr"/>
       <c r="O366" t="inlineStr"/>
@@ -36631,10 +36601,10 @@
         </is>
       </c>
       <c r="X366" t="n">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
       <c r="Y366" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z366" t="n">
         <v>0.78</v>
@@ -36646,7 +36616,7 @@
         <v>1</v>
       </c>
       <c r="AC366" t="n">
-        <v>0.5030000000000001</v>
+        <v>0.4455000000000001</v>
       </c>
       <c r="AD366" t="n">
         <v>1</v>
@@ -36698,7 +36668,7 @@
       <c r="K367" t="inlineStr"/>
       <c r="L367" t="inlineStr"/>
       <c r="M367" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N367" t="inlineStr"/>
       <c r="O367" t="inlineStr"/>
@@ -37398,7 +37368,7 @@
       <c r="K374" t="inlineStr"/>
       <c r="L374" t="inlineStr"/>
       <c r="M374" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N374" t="inlineStr"/>
       <c r="O374" t="inlineStr"/>
@@ -37431,10 +37401,10 @@
         </is>
       </c>
       <c r="X374" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="Y374" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="Z374" t="n">
         <v>0.46</v>
@@ -37446,7 +37416,7 @@
         <v>2</v>
       </c>
       <c r="AC374" t="n">
-        <v>0.4625</v>
+        <v>0.53</v>
       </c>
       <c r="AD374" t="n">
         <v>1</v>
@@ -37498,7 +37468,7 @@
       <c r="K375" t="inlineStr"/>
       <c r="L375" t="inlineStr"/>
       <c r="M375" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N375" t="inlineStr"/>
       <c r="O375" t="inlineStr"/>
@@ -37531,10 +37501,10 @@
         </is>
       </c>
       <c r="X375" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="Y375" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="Z375" t="n">
         <v>1</v>
@@ -37546,7 +37516,7 @@
         <v>1</v>
       </c>
       <c r="AC375" t="n">
-        <v>0.5045000000000001</v>
+        <v>0.5935</v>
       </c>
       <c r="AD375" t="n">
         <v>1</v>
@@ -37598,7 +37568,7 @@
       <c r="K376" t="inlineStr"/>
       <c r="L376" t="inlineStr"/>
       <c r="M376" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N376" t="inlineStr"/>
       <c r="O376" t="inlineStr"/>
@@ -37631,10 +37601,10 @@
         </is>
       </c>
       <c r="X376" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="Y376" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="Z376" t="n">
         <v>0.21</v>
@@ -37646,7 +37616,7 @@
         <v>3</v>
       </c>
       <c r="AC376" t="n">
-        <v>0.393</v>
+        <v>0.4605</v>
       </c>
       <c r="AD376" t="n">
         <v>1</v>
@@ -37698,7 +37668,7 @@
       <c r="K377" t="inlineStr"/>
       <c r="L377" t="inlineStr"/>
       <c r="M377" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="N377" t="inlineStr"/>
       <c r="O377" t="inlineStr"/>
@@ -37734,7 +37704,7 @@
         <v>0.85</v>
       </c>
       <c r="Y377" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="Z377" t="n">
         <v>0.59</v>
@@ -37746,7 +37716,7 @@
         <v>2</v>
       </c>
       <c r="AC377" t="n">
-        <v>0.6275000000000001</v>
+        <v>0.6345000000000001</v>
       </c>
       <c r="AD377" t="n">
         <v>1</v>
@@ -37798,7 +37768,7 @@
       <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr"/>
       <c r="M378" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="N378" t="inlineStr"/>
       <c r="O378" t="inlineStr"/>
@@ -37831,10 +37801,10 @@
         </is>
       </c>
       <c r="X378" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="Y378" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="Z378" t="n">
         <v>0.74</v>
@@ -37846,7 +37816,7 @@
         <v>3</v>
       </c>
       <c r="AC378" t="n">
-        <v>0.509</v>
+        <v>0.5215</v>
       </c>
       <c r="AD378" t="n">
         <v>1</v>
@@ -37898,7 +37868,7 @@
       <c r="K379" t="inlineStr"/>
       <c r="L379" t="inlineStr"/>
       <c r="M379" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="N379" t="inlineStr"/>
       <c r="O379" t="inlineStr"/>
@@ -37934,7 +37904,7 @@
         <v>0.85</v>
       </c>
       <c r="Y379" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="Z379" t="n">
         <v>1</v>
@@ -37946,7 +37916,7 @@
         <v>1</v>
       </c>
       <c r="AC379" t="n">
-        <v>0.801</v>
+        <v>0.8045000000000001</v>
       </c>
       <c r="AD379" t="n">
         <v>1</v>
@@ -37998,7 +37968,7 @@
       <c r="K380" t="inlineStr"/>
       <c r="L380" t="inlineStr"/>
       <c r="M380" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="N380" t="inlineStr"/>
       <c r="O380" t="inlineStr"/>
@@ -38031,10 +38001,10 @@
         </is>
       </c>
       <c r="X380" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="Y380" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="Z380" t="n">
         <v>0.51</v>
@@ -38046,7 +38016,7 @@
         <v>2</v>
       </c>
       <c r="AC380" t="n">
-        <v>0.676</v>
+        <v>0.6355000000000001</v>
       </c>
       <c r="AD380" t="n">
         <v>1</v>
@@ -38098,7 +38068,7 @@
       <c r="K381" t="inlineStr"/>
       <c r="L381" t="inlineStr"/>
       <c r="M381" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="N381" t="inlineStr"/>
       <c r="O381" t="inlineStr"/>
@@ -38131,10 +38101,10 @@
         </is>
       </c>
       <c r="X381" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="Y381" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="Z381" t="n">
         <v>1</v>
@@ -38146,7 +38116,7 @@
         <v>1</v>
       </c>
       <c r="AC381" t="n">
-        <v>0.828</v>
+        <v>0.7875</v>
       </c>
       <c r="AD381" t="n">
         <v>1</v>
@@ -38198,7 +38168,7 @@
       <c r="K382" t="inlineStr"/>
       <c r="L382" t="inlineStr"/>
       <c r="M382" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="N382" t="inlineStr"/>
       <c r="O382" t="inlineStr"/>
@@ -38231,10 +38201,10 @@
         </is>
       </c>
       <c r="X382" t="n">
-        <v>0.87</v>
+        <v>0.84</v>
       </c>
       <c r="Y382" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="Z382" t="n">
         <v>0.59</v>
@@ -38246,7 +38216,7 @@
         <v>3</v>
       </c>
       <c r="AC382" t="n">
-        <v>0.6619999999999999</v>
+        <v>0.6214999999999999</v>
       </c>
       <c r="AD382" t="n">
         <v>1</v>
@@ -38598,7 +38568,7 @@
       <c r="K386" t="inlineStr"/>
       <c r="L386" t="inlineStr"/>
       <c r="M386" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N386" t="inlineStr"/>
       <c r="O386" t="inlineStr"/>
@@ -38631,10 +38601,10 @@
         </is>
       </c>
       <c r="X386" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="Y386" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="Z386" t="n">
         <v>0.53</v>
@@ -38646,7 +38616,7 @@
         <v>3</v>
       </c>
       <c r="AC386" t="n">
-        <v>0.5675</v>
+        <v>0.5539999999999999</v>
       </c>
       <c r="AD386" t="n">
         <v>1</v>
@@ -38698,7 +38668,7 @@
       <c r="K387" t="inlineStr"/>
       <c r="L387" t="inlineStr"/>
       <c r="M387" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N387" t="inlineStr"/>
       <c r="O387" t="inlineStr"/>
@@ -38731,10 +38701,10 @@
         </is>
       </c>
       <c r="X387" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="Y387" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="Z387" t="n">
         <v>0.71</v>
@@ -38746,7 +38716,7 @@
         <v>2</v>
       </c>
       <c r="AC387" t="n">
-        <v>0.581</v>
+        <v>0.5644999999999999</v>
       </c>
       <c r="AD387" t="n">
         <v>1</v>
@@ -38798,7 +38768,7 @@
       <c r="K388" t="inlineStr"/>
       <c r="L388" t="inlineStr"/>
       <c r="M388" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N388" t="inlineStr"/>
       <c r="O388" t="inlineStr"/>
@@ -38831,10 +38801,10 @@
         </is>
       </c>
       <c r="X388" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="Y388" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="Z388" t="n">
         <v>1</v>
@@ -38846,7 +38816,7 @@
         <v>1</v>
       </c>
       <c r="AC388" t="n">
-        <v>0.777</v>
+        <v>0.7635</v>
       </c>
       <c r="AD388" t="n">
         <v>1</v>
@@ -38898,7 +38868,7 @@
       <c r="K389" t="inlineStr"/>
       <c r="L389" t="inlineStr"/>
       <c r="M389" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="N389" t="inlineStr"/>
       <c r="O389" t="inlineStr"/>
@@ -38931,10 +38901,10 @@
         </is>
       </c>
       <c r="X389" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="Y389" t="n">
-        <v>0.21</v>
+        <v>0.65</v>
       </c>
       <c r="Z389" t="n">
         <v>0.29</v>
@@ -38946,7 +38916,7 @@
         <v>3</v>
       </c>
       <c r="AC389" t="n">
-        <v>0.373</v>
+        <v>0.572</v>
       </c>
       <c r="AD389" t="n">
         <v>1</v>
@@ -38998,7 +38968,7 @@
       <c r="K390" t="inlineStr"/>
       <c r="L390" t="inlineStr"/>
       <c r="M390" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="N390" t="inlineStr"/>
       <c r="O390" t="inlineStr"/>
@@ -39031,10 +39001,10 @@
         </is>
       </c>
       <c r="X390" t="n">
-        <v>0.34</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Y390" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="Z390" t="n">
         <v>1</v>
@@ -39043,10 +39013,10 @@
         <v>1</v>
       </c>
       <c r="AB390" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC390" t="n">
-        <v>0.5045000000000001</v>
+        <v>0.774</v>
       </c>
       <c r="AD390" t="n">
         <v>1</v>
@@ -39098,7 +39068,7 @@
       <c r="K391" t="inlineStr"/>
       <c r="L391" t="inlineStr"/>
       <c r="M391" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="N391" t="inlineStr"/>
       <c r="O391" t="inlineStr"/>
@@ -39131,10 +39101,10 @@
         </is>
       </c>
       <c r="X391" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="Y391" t="n">
-        <v>0.15</v>
+        <v>0.62</v>
       </c>
       <c r="Z391" t="n">
         <v>0.74</v>
@@ -39143,10 +39113,10 @@
         <v>0.62</v>
       </c>
       <c r="AB391" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC391" t="n">
-        <v>0.5125</v>
+        <v>0.722</v>
       </c>
       <c r="AD391" t="n">
         <v>1</v>
@@ -39498,7 +39468,7 @@
       <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr"/>
       <c r="M395" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="N395" t="inlineStr"/>
       <c r="O395" t="inlineStr"/>
@@ -39531,10 +39501,10 @@
         </is>
       </c>
       <c r="X395" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="Y395" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="Z395" t="n">
         <v>0.63</v>
@@ -39546,7 +39516,7 @@
         <v>2</v>
       </c>
       <c r="AC395" t="n">
-        <v>0.655</v>
+        <v>0.6685000000000001</v>
       </c>
       <c r="AD395" t="n">
         <v>1</v>
@@ -39598,7 +39568,7 @@
       <c r="K396" t="inlineStr"/>
       <c r="L396" t="inlineStr"/>
       <c r="M396" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="N396" t="inlineStr"/>
       <c r="O396" t="inlineStr"/>
@@ -39631,10 +39601,10 @@
         </is>
       </c>
       <c r="X396" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="Y396" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="Z396" t="n">
         <v>0.74</v>
@@ -39646,7 +39616,7 @@
         <v>3</v>
       </c>
       <c r="AC396" t="n">
-        <v>0.5345</v>
+        <v>0.5599999999999999</v>
       </c>
       <c r="AD396" t="n">
         <v>1</v>
@@ -39698,7 +39668,7 @@
       <c r="K397" t="inlineStr"/>
       <c r="L397" t="inlineStr"/>
       <c r="M397" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="N397" t="inlineStr"/>
       <c r="O397" t="inlineStr"/>
@@ -39731,10 +39701,10 @@
         </is>
       </c>
       <c r="X397" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="Y397" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="Z397" t="n">
         <v>1</v>
@@ -39746,7 +39716,7 @@
         <v>1</v>
       </c>
       <c r="AC397" t="n">
-        <v>0.8145000000000001</v>
+        <v>0.828</v>
       </c>
       <c r="AD397" t="n">
         <v>1</v>
@@ -39798,7 +39768,7 @@
       <c r="K398" t="inlineStr"/>
       <c r="L398" t="inlineStr"/>
       <c r="M398" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="N398" t="inlineStr"/>
       <c r="O398" t="inlineStr"/>
@@ -39831,10 +39801,10 @@
         </is>
       </c>
       <c r="X398" t="n">
-        <v>0.76</v>
+        <v>0</v>
       </c>
       <c r="Y398" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="Z398" t="n">
         <v>1</v>
@@ -39843,10 +39813,10 @@
         <v>1</v>
       </c>
       <c r="AB398" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC398" t="n">
-        <v>0.8929999999999999</v>
+        <v>0.4585</v>
       </c>
       <c r="AD398" t="n">
         <v>1</v>
@@ -39898,7 +39868,7 @@
       <c r="K399" t="inlineStr"/>
       <c r="L399" t="inlineStr"/>
       <c r="M399" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="N399" t="inlineStr"/>
       <c r="O399" t="inlineStr"/>
@@ -39931,10 +39901,10 @@
         </is>
       </c>
       <c r="X399" t="n">
-        <v>0.97</v>
+        <v>0.76</v>
       </c>
       <c r="Y399" t="n">
-        <v>0.91</v>
+        <v>0.36</v>
       </c>
       <c r="Z399" t="n">
         <v>0.47</v>
@@ -39943,10 +39913,10 @@
         <v>0.48</v>
       </c>
       <c r="AB399" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC399" t="n">
-        <v>0.7754999999999999</v>
+        <v>0.5199999999999999</v>
       </c>
       <c r="AD399" t="n">
         <v>1</v>
@@ -39998,7 +39968,7 @@
       <c r="K400" t="inlineStr"/>
       <c r="L400" t="inlineStr"/>
       <c r="M400" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="N400" t="inlineStr"/>
       <c r="O400" t="inlineStr"/>
@@ -40031,10 +40001,10 @@
         </is>
       </c>
       <c r="X400" t="n">
-        <v>0.97</v>
+        <v>0.76</v>
       </c>
       <c r="Y400" t="n">
-        <v>0.9</v>
+        <v>0.31</v>
       </c>
       <c r="Z400" t="n">
         <v>0.74</v>
@@ -40043,10 +40013,10 @@
         <v>0.62</v>
       </c>
       <c r="AB400" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC400" t="n">
-        <v>0.847</v>
+        <v>0.5774999999999999</v>
       </c>
       <c r="AD400" t="n">
         <v>1</v>
@@ -40098,7 +40068,7 @@
       <c r="K401" t="inlineStr"/>
       <c r="L401" t="inlineStr"/>
       <c r="M401" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N401" t="inlineStr"/>
       <c r="O401" t="inlineStr"/>
@@ -40131,10 +40101,10 @@
         </is>
       </c>
       <c r="X401" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="Y401" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z401" t="n">
         <v>0.62</v>
@@ -40146,7 +40116,7 @@
         <v>2</v>
       </c>
       <c r="AC401" t="n">
-        <v>0.4365</v>
+        <v>0.394</v>
       </c>
       <c r="AD401" t="n">
         <v>1</v>
@@ -40198,7 +40168,7 @@
       <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr"/>
       <c r="M402" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N402" t="inlineStr"/>
       <c r="O402" t="inlineStr"/>
@@ -40231,7 +40201,7 @@
         </is>
       </c>
       <c r="X402" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="Y402" t="n">
         <v>0</v>
@@ -40246,7 +40216,7 @@
         <v>1</v>
       </c>
       <c r="AC402" t="n">
-        <v>0.545</v>
+        <v>0.527</v>
       </c>
       <c r="AD402" t="n">
         <v>1</v>
@@ -40298,7 +40268,7 @@
       <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr"/>
       <c r="M403" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="N403" t="inlineStr"/>
       <c r="O403" t="inlineStr"/>
@@ -40331,7 +40301,7 @@
         </is>
       </c>
       <c r="X403" t="n">
-        <v>0.65</v>
+        <v>0.59</v>
       </c>
       <c r="Y403" t="n">
         <v>0</v>
@@ -40346,7 +40316,7 @@
         <v>3</v>
       </c>
       <c r="AC403" t="n">
-        <v>0.3635</v>
+        <v>0.3455</v>
       </c>
       <c r="AD403" t="n">
         <v>1</v>
@@ -40398,7 +40368,7 @@
       <c r="K404" t="inlineStr"/>
       <c r="L404" t="inlineStr"/>
       <c r="M404" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N404" t="inlineStr"/>
       <c r="O404" t="inlineStr"/>
@@ -40431,10 +40401,10 @@
         </is>
       </c>
       <c r="X404" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Y404" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="Z404" t="n">
         <v>0.55</v>
@@ -40446,7 +40416,7 @@
         <v>3</v>
       </c>
       <c r="AC404" t="n">
-        <v>0.6045</v>
+        <v>0.591</v>
       </c>
       <c r="AD404" t="n">
         <v>1</v>
@@ -40498,7 +40468,7 @@
       <c r="K405" t="inlineStr"/>
       <c r="L405" t="inlineStr"/>
       <c r="M405" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N405" t="inlineStr"/>
       <c r="O405" t="inlineStr"/>
@@ -40531,10 +40501,10 @@
         </is>
       </c>
       <c r="X405" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Y405" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="Z405" t="n">
         <v>1</v>
@@ -40546,7 +40516,7 @@
         <v>1</v>
       </c>
       <c r="AC405" t="n">
-        <v>0.804</v>
+        <v>0.7905000000000001</v>
       </c>
       <c r="AD405" t="n">
         <v>1</v>
@@ -40598,7 +40568,7 @@
       <c r="K406" t="inlineStr"/>
       <c r="L406" t="inlineStr"/>
       <c r="M406" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N406" t="inlineStr"/>
       <c r="O406" t="inlineStr"/>
@@ -40631,10 +40601,10 @@
         </is>
       </c>
       <c r="X406" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="Y406" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="Z406" t="n">
         <v>0.82</v>
@@ -40646,7 +40616,7 @@
         <v>2</v>
       </c>
       <c r="AC406" t="n">
-        <v>0.66</v>
+        <v>0.6435</v>
       </c>
       <c r="AD406" t="n">
         <v>1</v>
@@ -40704,7 +40674,7 @@
         <v>1.5</v>
       </c>
       <c r="O407" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P407" t="n">
         <v>120</v>
@@ -40802,7 +40772,7 @@
         <v>1.5</v>
       </c>
       <c r="O408" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P408" t="n">
         <v>120</v>
@@ -40900,7 +40870,7 @@
         <v>1.5</v>
       </c>
       <c r="O409" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P409" t="n">
         <v>120</v>
@@ -42759,7 +42729,7 @@
       <c r="L428" t="inlineStr"/>
       <c r="M428" t="inlineStr"/>
       <c r="N428" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O428" t="n">
         <v>50</v>
@@ -42787,7 +42757,7 @@
         </is>
       </c>
       <c r="X428" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="Y428" t="n">
         <v>1</v>
@@ -42799,10 +42769,10 @@
         <v>0.22</v>
       </c>
       <c r="AB428" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC428" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.7729999999999999</v>
       </c>
       <c r="AD428" t="n">
         <v>1</v>
@@ -42857,7 +42827,7 @@
       <c r="L429" t="inlineStr"/>
       <c r="M429" t="inlineStr"/>
       <c r="N429" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O429" t="n">
         <v>50</v>
@@ -42885,22 +42855,22 @@
         </is>
       </c>
       <c r="X429" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="Y429" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="Z429" t="n">
         <v>0.74</v>
       </c>
       <c r="AA429" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="AB429" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC429" t="n">
-        <v>0.8059999999999999</v>
+        <v>0.702</v>
       </c>
       <c r="AD429" t="n">
         <v>1</v>
@@ -42955,7 +42925,7 @@
       <c r="L430" t="inlineStr"/>
       <c r="M430" t="inlineStr"/>
       <c r="N430" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O430" t="n">
         <v>50</v>
@@ -42983,10 +42953,10 @@
         </is>
       </c>
       <c r="X430" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="Y430" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z430" t="n">
         <v>0.89</v>
@@ -42998,7 +42968,7 @@
         <v>3</v>
       </c>
       <c r="AC430" t="n">
-        <v>0.7585</v>
+        <v>0.6775</v>
       </c>
       <c r="AD430" t="n">
         <v>1</v>
@@ -43347,7 +43317,7 @@
       <c r="L434" t="inlineStr"/>
       <c r="M434" t="inlineStr"/>
       <c r="N434" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O434" t="n">
         <v>50</v>
@@ -43445,7 +43415,7 @@
       <c r="L435" t="inlineStr"/>
       <c r="M435" t="inlineStr"/>
       <c r="N435" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O435" t="n">
         <v>50</v>
@@ -43543,7 +43513,7 @@
       <c r="L436" t="inlineStr"/>
       <c r="M436" t="inlineStr"/>
       <c r="N436" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O436" t="n">
         <v>50</v>
@@ -43571,10 +43541,10 @@
         </is>
       </c>
       <c r="X436" t="n">
-        <v>0.17</v>
+        <v>0.05</v>
       </c>
       <c r="Y436" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="Z436" t="n">
         <v>0.86</v>
@@ -43586,7 +43556,7 @@
         <v>1</v>
       </c>
       <c r="AC436" t="n">
-        <v>0.4075</v>
+        <v>0.3365</v>
       </c>
       <c r="AD436" t="n">
         <v>1</v>
@@ -43641,10 +43611,10 @@
       <c r="L437" t="inlineStr"/>
       <c r="M437" t="inlineStr"/>
       <c r="N437" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O437" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P437" t="n">
         <v>120</v>
@@ -43669,10 +43639,10 @@
         </is>
       </c>
       <c r="X437" t="n">
-        <v>0.23</v>
+        <v>0.43</v>
       </c>
       <c r="Y437" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="Z437" t="n">
         <v>0.88</v>
@@ -43684,7 +43654,7 @@
         <v>1</v>
       </c>
       <c r="AC437" t="n">
-        <v>0.3305</v>
+        <v>0.4815</v>
       </c>
       <c r="AD437" t="n">
         <v>1</v>
@@ -43739,10 +43709,10 @@
       <c r="L438" t="inlineStr"/>
       <c r="M438" t="inlineStr"/>
       <c r="N438" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O438" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P438" t="n">
         <v>120</v>
@@ -43767,7 +43737,7 @@
         </is>
       </c>
       <c r="X438" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="Y438" t="n">
         <v>0</v>
@@ -43782,7 +43752,7 @@
         <v>2</v>
       </c>
       <c r="AC438" t="n">
-        <v>0.188</v>
+        <v>0.212</v>
       </c>
       <c r="AD438" t="n">
         <v>1</v>
@@ -43837,10 +43807,10 @@
       <c r="L439" t="inlineStr"/>
       <c r="M439" t="inlineStr"/>
       <c r="N439" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="O439" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="P439" t="n">
         <v>120</v>
@@ -45111,7 +45081,7 @@
       <c r="L452" t="inlineStr"/>
       <c r="M452" t="inlineStr"/>
       <c r="N452" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O452" t="n">
         <v>80</v>
@@ -45209,7 +45179,7 @@
       <c r="L453" t="inlineStr"/>
       <c r="M453" t="inlineStr"/>
       <c r="N453" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O453" t="n">
         <v>80</v>
@@ -45307,7 +45277,7 @@
       <c r="L454" t="inlineStr"/>
       <c r="M454" t="inlineStr"/>
       <c r="N454" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O454" t="n">
         <v>80</v>
@@ -45699,7 +45669,7 @@
       <c r="L458" t="inlineStr"/>
       <c r="M458" t="inlineStr"/>
       <c r="N458" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O458" t="n">
         <v>50</v>
@@ -45727,10 +45697,10 @@
         </is>
       </c>
       <c r="X458" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="Y458" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="Z458" t="n">
         <v>0.88</v>
@@ -45742,7 +45712,7 @@
         <v>1</v>
       </c>
       <c r="AC458" t="n">
-        <v>0.406</v>
+        <v>0.3305</v>
       </c>
       <c r="AD458" t="n">
         <v>1</v>
@@ -45797,7 +45767,7 @@
       <c r="L459" t="inlineStr"/>
       <c r="M459" t="inlineStr"/>
       <c r="N459" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O459" t="n">
         <v>50</v>
@@ -45825,7 +45795,7 @@
         </is>
       </c>
       <c r="X459" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="Y459" t="n">
         <v>0</v>
@@ -45840,7 +45810,7 @@
         <v>2</v>
       </c>
       <c r="AC459" t="n">
-        <v>0.2145</v>
+        <v>0.2115</v>
       </c>
       <c r="AD459" t="n">
         <v>1</v>
@@ -45895,7 +45865,7 @@
       <c r="L460" t="inlineStr"/>
       <c r="M460" t="inlineStr"/>
       <c r="N460" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O460" t="n">
         <v>50</v>
@@ -45996,7 +45966,7 @@
         <v>1.5</v>
       </c>
       <c r="O461" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P461" t="n">
         <v>120</v>
@@ -46094,7 +46064,7 @@
         <v>1.5</v>
       </c>
       <c r="O462" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P462" t="n">
         <v>120</v>
@@ -46192,7 +46162,7 @@
         <v>1.5</v>
       </c>
       <c r="O463" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="P463" t="n">
         <v>120</v>
@@ -46584,7 +46554,7 @@
         <v>2.75</v>
       </c>
       <c r="O467" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P467" t="n">
         <v>120</v>
@@ -46682,7 +46652,7 @@
         <v>2.75</v>
       </c>
       <c r="O468" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P468" t="n">
         <v>120</v>
@@ -46780,7 +46750,7 @@
         <v>2.75</v>
       </c>
       <c r="O469" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="P469" t="n">
         <v>120</v>
@@ -46875,7 +46845,7 @@
       <c r="L470" t="inlineStr"/>
       <c r="M470" t="inlineStr"/>
       <c r="N470" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O470" t="n">
         <v>35</v>
@@ -46903,22 +46873,22 @@
         </is>
       </c>
       <c r="X470" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="Y470" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z470" t="n">
         <v>0.92</v>
       </c>
       <c r="AA470" t="n">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="AB470" t="n">
         <v>3</v>
       </c>
       <c r="AC470" t="n">
-        <v>0.6715000000000001</v>
+        <v>0.7989999999999999</v>
       </c>
       <c r="AD470" t="n">
         <v>1</v>
@@ -46973,7 +46943,7 @@
       <c r="L471" t="inlineStr"/>
       <c r="M471" t="inlineStr"/>
       <c r="N471" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O471" t="n">
         <v>35</v>
@@ -47001,10 +46971,10 @@
         </is>
       </c>
       <c r="X471" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="Y471" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="Z471" t="n">
         <v>0.74</v>
@@ -47016,7 +46986,7 @@
         <v>2</v>
       </c>
       <c r="AC471" t="n">
-        <v>0.7975</v>
+        <v>0.8335</v>
       </c>
       <c r="AD471" t="n">
         <v>1</v>
@@ -47071,7 +47041,7 @@
       <c r="L472" t="inlineStr"/>
       <c r="M472" t="inlineStr"/>
       <c r="N472" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O472" t="n">
         <v>35</v>
@@ -47099,10 +47069,10 @@
         </is>
       </c>
       <c r="X472" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="Y472" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="Z472" t="n">
         <v>1</v>
@@ -47114,7 +47084,7 @@
         <v>1</v>
       </c>
       <c r="AC472" t="n">
-        <v>0.8190000000000001</v>
+        <v>0.8815000000000001</v>
       </c>
       <c r="AD472" t="n">
         <v>1</v>
@@ -49521,7 +49491,7 @@
       <c r="L497" t="inlineStr"/>
       <c r="M497" t="inlineStr"/>
       <c r="N497" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O497" t="n">
         <v>35</v>
@@ -49549,22 +49519,22 @@
         </is>
       </c>
       <c r="X497" t="n">
-        <v>0.53</v>
+        <v>0.68</v>
       </c>
       <c r="Y497" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z497" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="AA497" t="n">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="AB497" t="n">
         <v>3</v>
       </c>
       <c r="AC497" t="n">
-        <v>0.6365000000000001</v>
+        <v>0.7729999999999999</v>
       </c>
       <c r="AD497" t="n">
         <v>1</v>
@@ -49619,7 +49589,7 @@
       <c r="L498" t="inlineStr"/>
       <c r="M498" t="inlineStr"/>
       <c r="N498" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O498" t="n">
         <v>35</v>
@@ -49647,10 +49617,10 @@
         </is>
       </c>
       <c r="X498" t="n">
-        <v>0.88</v>
+        <v>0.95</v>
       </c>
       <c r="Y498" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="Z498" t="n">
         <v>0.68</v>
@@ -49662,7 +49632,7 @@
         <v>2</v>
       </c>
       <c r="AC498" t="n">
-        <v>0.7675</v>
+        <v>0.8095</v>
       </c>
       <c r="AD498" t="n">
         <v>1</v>
@@ -49717,7 +49687,7 @@
       <c r="L499" t="inlineStr"/>
       <c r="M499" t="inlineStr"/>
       <c r="N499" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O499" t="n">
         <v>35</v>
@@ -49745,10 +49715,10 @@
         </is>
       </c>
       <c r="X499" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="Y499" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="Z499" t="n">
         <v>0.9</v>
@@ -49760,7 +49730,7 @@
         <v>1</v>
       </c>
       <c r="AC499" t="n">
-        <v>0.772</v>
+        <v>0.8405</v>
       </c>
       <c r="AD499" t="n">
         <v>1</v>
@@ -51876,7 +51846,7 @@
         <v>1.5</v>
       </c>
       <c r="O521" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P521" t="n">
         <v>120</v>
@@ -51974,7 +51944,7 @@
         <v>1.5</v>
       </c>
       <c r="O522" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P522" t="n">
         <v>120</v>
@@ -52072,7 +52042,7 @@
         <v>1.5</v>
       </c>
       <c r="O523" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="P523" t="n">
         <v>120</v>
@@ -52106,13 +52076,13 @@
         <v>0.9</v>
       </c>
       <c r="AA523" t="n">
-        <v>0.76</v>
+        <v>0.46</v>
       </c>
       <c r="AB523" t="n">
         <v>1</v>
       </c>
       <c r="AC523" t="n">
-        <v>0.8435</v>
+        <v>0.7985</v>
       </c>
       <c r="AD523" t="n">
         <v>1</v>
@@ -52758,7 +52728,7 @@
         <v>1.5</v>
       </c>
       <c r="O530" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P530" t="n">
         <v>120</v>
@@ -52856,7 +52826,7 @@
         <v>1.5</v>
       </c>
       <c r="O531" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P531" t="n">
         <v>120</v>
@@ -52954,7 +52924,7 @@
         <v>1.5</v>
       </c>
       <c r="O532" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P532" t="n">
         <v>120</v>
@@ -54225,7 +54195,7 @@
       <c r="L545" t="inlineStr"/>
       <c r="M545" t="inlineStr"/>
       <c r="N545" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O545" t="n">
         <v>50</v>
@@ -54265,7 +54235,7 @@
         <v>0.15</v>
       </c>
       <c r="AB545" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC545" t="n">
         <v>0.6764999999999999</v>
@@ -54323,7 +54293,7 @@
       <c r="L546" t="inlineStr"/>
       <c r="M546" t="inlineStr"/>
       <c r="N546" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O546" t="n">
         <v>50</v>
@@ -54351,10 +54321,10 @@
         </is>
       </c>
       <c r="X546" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Y546" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z546" t="n">
         <v>0.9399999999999999</v>
@@ -54363,10 +54333,10 @@
         <v>0.67</v>
       </c>
       <c r="AB546" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC546" t="n">
-        <v>0.6395</v>
+        <v>0.737</v>
       </c>
       <c r="AD546" t="n">
         <v>1</v>
@@ -54421,7 +54391,7 @@
       <c r="L547" t="inlineStr"/>
       <c r="M547" t="inlineStr"/>
       <c r="N547" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O547" t="n">
         <v>50</v>
@@ -54449,10 +54419,10 @@
         </is>
       </c>
       <c r="X547" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="Y547" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="Z547" t="n">
         <v>0.77</v>
@@ -54464,7 +54434,7 @@
         <v>1</v>
       </c>
       <c r="AC547" t="n">
-        <v>0.7785</v>
+        <v>0.8270000000000001</v>
       </c>
       <c r="AD547" t="n">
         <v>1</v>
@@ -54813,7 +54783,7 @@
       <c r="L551" t="inlineStr"/>
       <c r="M551" t="inlineStr"/>
       <c r="N551" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O551" t="n">
         <v>50</v>
@@ -54841,10 +54811,10 @@
         </is>
       </c>
       <c r="X551" t="n">
-        <v>0.67</v>
+        <v>0.52</v>
       </c>
       <c r="Y551" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="Z551" t="n">
         <v>0.9399999999999999</v>
@@ -54856,7 +54826,7 @@
         <v>3</v>
       </c>
       <c r="AC551" t="n">
-        <v>0.7310000000000001</v>
+        <v>0.6335</v>
       </c>
       <c r="AD551" t="n">
         <v>1</v>
@@ -54911,7 +54881,7 @@
       <c r="L552" t="inlineStr"/>
       <c r="M552" t="inlineStr"/>
       <c r="N552" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O552" t="n">
         <v>50</v>
@@ -54939,10 +54909,10 @@
         </is>
       </c>
       <c r="X552" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="Y552" t="n">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="Z552" t="n">
         <v>0.68</v>
@@ -54951,10 +54921,10 @@
         <v>0.35</v>
       </c>
       <c r="AB552" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC552" t="n">
-        <v>0.8064999999999999</v>
+        <v>0.7675</v>
       </c>
       <c r="AD552" t="n">
         <v>1</v>
@@ -55009,7 +54979,7 @@
       <c r="L553" t="inlineStr"/>
       <c r="M553" t="inlineStr"/>
       <c r="N553" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O553" t="n">
         <v>50</v>
@@ -55037,10 +55007,10 @@
         </is>
       </c>
       <c r="X553" t="n">
-        <v>0.83</v>
+        <v>0.72</v>
       </c>
       <c r="Y553" t="n">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="Z553" t="n">
         <v>0.89</v>
@@ -55049,10 +55019,10 @@
         <v>0.76</v>
       </c>
       <c r="AB553" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC553" t="n">
-        <v>0.8385</v>
+        <v>0.767</v>
       </c>
       <c r="AD553" t="n">
         <v>1</v>
@@ -55989,7 +55959,7 @@
       <c r="L563" t="inlineStr"/>
       <c r="M563" t="inlineStr"/>
       <c r="N563" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O563" t="n">
         <v>35</v>
@@ -56017,10 +55987,10 @@
         </is>
       </c>
       <c r="X563" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="Y563" t="n">
-        <v>0.54</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="Z563" t="n">
         <v>0.95</v>
@@ -56032,7 +56002,7 @@
         <v>3</v>
       </c>
       <c r="AC563" t="n">
-        <v>0.6025</v>
+        <v>0.712</v>
       </c>
       <c r="AD563" t="n">
         <v>1</v>
@@ -56087,7 +56057,7 @@
       <c r="L564" t="inlineStr"/>
       <c r="M564" t="inlineStr"/>
       <c r="N564" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O564" t="n">
         <v>35</v>
@@ -56115,10 +56085,10 @@
         </is>
       </c>
       <c r="X564" t="n">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="Y564" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="Z564" t="n">
         <v>0.67</v>
@@ -56127,10 +56097,10 @@
         <v>0.35</v>
       </c>
       <c r="AB564" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC564" t="n">
-        <v>0.7534999999999999</v>
+        <v>0.7955</v>
       </c>
       <c r="AD564" t="n">
         <v>1</v>
@@ -56185,7 +56155,7 @@
       <c r="L565" t="inlineStr"/>
       <c r="M565" t="inlineStr"/>
       <c r="N565" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O565" t="n">
         <v>35</v>
@@ -56213,10 +56183,10 @@
         </is>
       </c>
       <c r="X565" t="n">
-        <v>0.66</v>
+        <v>0.78</v>
       </c>
       <c r="Y565" t="n">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="Z565" t="n">
         <v>0.87</v>
@@ -56225,10 +56195,10 @@
         <v>0.76</v>
       </c>
       <c r="AB565" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC565" t="n">
-        <v>0.745</v>
+        <v>0.8195</v>
       </c>
       <c r="AD565" t="n">
         <v>1</v>
@@ -57168,7 +57138,7 @@
         <v>1.5</v>
       </c>
       <c r="O575" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P575" t="n">
         <v>120</v>
@@ -57266,7 +57236,7 @@
         <v>1.5</v>
       </c>
       <c r="O576" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P576" t="n">
         <v>120</v>
@@ -57364,7 +57334,7 @@
         <v>1.5</v>
       </c>
       <c r="O577" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="P577" t="n">
         <v>120</v>
